--- a/saidas/ordens_dia/ordem_dia_2026_07_29_executor_v5_5.xlsx
+++ b/saidas/ordens_dia/ordem_dia_2026_07_29_executor_v5_5.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DE5"/>
+  <dimension ref="A1:DE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -981,11 +981,11 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>GOAU4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1020,40 +1020,40 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>186</v>
+        <v>114</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4079</v>
+        <v>0.2495</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6774</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3564</v>
+        <v>0.3793</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.7677</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1563</v>
+        <v>0.3161</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1232</v>
+        <v>0.0615</v>
       </c>
       <c r="R2" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1624</v>
+        <v>0.3719</v>
       </c>
       <c r="T2" t="n">
-        <v>398</v>
+        <v>267</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2444</v>
+        <v>0.1909</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0489</v>
+        <v>0.0518</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -1067,49 +1067,49 @@
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>0.3277</v>
+        <v>0.259</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.024</v>
+        <v>0.8094</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2434</v>
+        <v>0.1899</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.3277</v>
+        <v>0.259</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0668</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.0919</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1455</v>
+        <v>0.1303</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.0136</v>
+        <v>0.0158</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.3076</v>
+        <v>0.3362</v>
       </c>
       <c r="AI2" t="n">
-        <v>18.77</v>
+        <v>10.77</v>
       </c>
       <c r="AJ2" t="n">
-        <v>19.36</v>
+        <v>11.17</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.0997</v>
+        <v>0.0476</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.054728</v>
+        <v>0.118415</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.106818</v>
+        <v>1.128108</v>
       </c>
       <c r="AN2" t="n">
-        <v>10.68</v>
+        <v>12.81</v>
       </c>
       <c r="AO2" t="n">
         <v>1</v>
@@ -1124,13 +1124,13 @@
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.056484</v>
+        <v>1.119918</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.159717</v>
+        <v>1.191264</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.633136</v>
+        <v>0.874264</v>
       </c>
       <c r="AV2" t="n">
         <v>1</v>
@@ -1139,10 +1139,10 @@
         <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.037963</v>
+        <v>0.044087</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.4416</v>
+        <v>2.686</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -1200,13 +1200,13 @@
         <v>1</v>
       </c>
       <c r="BO2" t="n">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="BP2" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.9494949494949495</v>
+        <v>0.6464646464646464</v>
       </c>
       <c r="BR2" t="n">
         <v>1</v>
@@ -1228,43 +1228,43 @@
         </is>
       </c>
       <c r="BW2" t="n">
-        <v>0.6935</v>
+        <v>0.6917</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.6574</v>
+        <v>0.6235000000000001</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.5596</v>
+        <v>0.5051</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.4205586974811158</v>
+        <v>0.3600266258768599</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.5872601307644413</v>
+        <v>0.5231262931542173</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.7199832034886435</v>
+        <v>0.6308080237461189</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.7199832034886435</v>
+        <v>0.6308080237461189</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.6461538461538462</v>
+        <v>0.4137931034482759</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.3134328358208955</v>
+        <v>0.3302752293577982</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.5518518518518518</v>
+        <v>0.6187050359712231</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.93125</v>
+        <v>0.5548387096774193</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.412280701754386</v>
+        <v>0.3106060606060606</v>
       </c>
       <c r="CJ2" t="n">
         <v>0</v>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.5767</v>
+        <v>0.5923</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.5767</v>
+        <v>0.5923</v>
       </c>
       <c r="CS2" t="n">
         <v>0</v>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>naked_30: esp=+0.243 | spread_35_20: esp=+0.070 | spread_45_25: esp=+0.092 | spread_45_15: esp=+0.145</t>
+          <t>naked_30: esp=+0.190 | spread_35_20: esp=+0.067 | spread_45_25: esp=+0.078 | spread_45_15: esp=+0.130</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>[Empírico] Call delta~45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.328 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>[Empírico] Call delta~45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.259 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1405,40 +1405,40 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1031</v>
+        <v>0.105</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8298</v>
+        <v>0.8333</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4426</v>
+        <v>0.4516</v>
       </c>
       <c r="O3" t="n">
-        <v>1.286</v>
+        <v>1.2835</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7336</v>
+        <v>0.7368</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.059</v>
+        <v>-0.0485</v>
       </c>
       <c r="R3" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0101</v>
+        <v>0.0118</v>
       </c>
       <c r="T3" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6526999999999999</v>
+        <v>0.6643</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1187</v>
+        <v>0.117</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -1452,49 +1452,49 @@
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.8267</v>
+        <v>0.8399</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.5833</v>
+        <v>2.6248</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.6633</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8267</v>
+        <v>0.8399</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.1626</v>
+        <v>0.166</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.2106</v>
+        <v>0.2136</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3251</v>
+        <v>0.331</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0395</v>
+        <v>0.0378</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.2112</v>
+        <v>0.1881</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.0673</v>
+        <v>0.0698</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.213894</v>
+        <v>-0.208582</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.154009</v>
+        <v>1.181753</v>
       </c>
       <c r="AN3" t="n">
-        <v>15.4</v>
+        <v>18.18</v>
       </c>
       <c r="AO3" t="n">
         <v>1</v>
@@ -1524,10 +1524,10 @@
         <v>-1</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.110244</v>
+        <v>0.105469</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.9402</v>
+        <v>1.9777</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1675,10 +1675,10 @@
         <v>1</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.6287</v>
+        <v>0.6371</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.6287</v>
+        <v>0.6371</v>
       </c>
       <c r="CS3" t="n">
         <v>0</v>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>naked_30: esp=+0.652 | spread_35_20: esp=+0.163 | spread_45_25: esp=+0.211 | spread_45_15: esp=+0.325</t>
+          <t>naked_30: esp=+0.663 | spread_35_20: esp=+0.166 | spread_45_25: esp=+0.214 | spread_45_15: esp=+0.331</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.827 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.840 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1789,37 +1789,37 @@
         <v>43</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.0941</v>
       </c>
       <c r="M4" t="n">
         <v>0.6512</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0702</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2666</v>
+        <v>0.2667</v>
       </c>
       <c r="P4" t="n">
         <v>-0.18</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.058</v>
+        <v>-0.0437</v>
       </c>
       <c r="R4" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0722</v>
+        <v>-0.0717</v>
       </c>
       <c r="T4" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="U4" t="n">
         <v>-0.1354</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0178</v>
+        <v>0.0177</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1858,28 +1858,28 @@
         <v>-0.1207</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.011</v>
+        <v>0.0106</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.2226</v>
+        <v>0.1902</v>
       </c>
       <c r="AI4" t="n">
         <v>18.04</v>
       </c>
       <c r="AJ4" t="n">
-        <v>18.5</v>
+        <v>18.48</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.0128</v>
+        <v>-0.0127</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.053343</v>
+        <v>0.042047</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.159549</v>
+        <v>1.17222</v>
       </c>
       <c r="AN4" t="n">
-        <v>15.95</v>
+        <v>17.22</v>
       </c>
       <c r="AO4" t="n">
         <v>1</v>
@@ -1909,10 +1909,10 @@
         <v>1</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.030743</v>
+        <v>0.029493</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.7351</v>
+        <v>1.4256</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -2060,10 +2060,10 @@
         <v>0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.5809</v>
+        <v>0.5564</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.5809</v>
+        <v>0.5564</v>
       </c>
       <c r="CS4" t="n">
         <v>1</v>
@@ -2092,363 +2092,6 @@
       <c r="DC4" t="inlineStr"/>
       <c r="DD4" t="inlineStr"/>
       <c r="DE4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>v5.5_executor_diario</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>46231</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>USIM5</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Alerta CALL (VETADA)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>VETADA — esperança histórica insuficiente</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>alerta_executor_nivel_B</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>57</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.5263</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.1475</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.5541</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.0184</v>
-      </c>
-      <c r="R5" t="n">
-        <v>436</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-0.0692</v>
-      </c>
-      <c r="T5" t="n">
-        <v>335</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-0.0577</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.0499</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>nenhuma</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>esperanca</t>
-        </is>
-      </c>
-      <c r="Z5" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-0.0587</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-0.0639</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-0.0404</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-0.0323</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-0.0561</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0.0233</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.2293</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>8.69</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>9.16</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-0.0072</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0.06879</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.143976</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1.139753</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.139753</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0.845253</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0.06489499999999999</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>forte</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>expansao</t>
-        </is>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="BI5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>38</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>65</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>0.3535353535353535</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>exec_bilateral</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>expansion_moderada</t>
-        </is>
-      </c>
-      <c r="BW5" t="n">
-        <v>0.6584</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>0.6328</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>0.5611</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>0.4382483987992929</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0.5747077669640731</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>0.3957849185932791</v>
-      </c>
-      <c r="CC5" t="n">
-        <v>0.5747077669640731</v>
-      </c>
-      <c r="CD5" t="n">
-        <v>0.5943396226415094</v>
-      </c>
-      <c r="CE5" t="n">
-        <v>0.4436619718309859</v>
-      </c>
-      <c r="CF5" t="n">
-        <v>0.6509433962264151</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>0.4339622641509434</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="CI5" t="n">
-        <v>0.07843137254901961</v>
-      </c>
-      <c r="CJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK5" t="inlineStr">
-        <is>
-          <t>expansao_moderada_sem_exec_forte</t>
-        </is>
-      </c>
-      <c r="CL5" t="inlineStr">
-        <is>
-          <t>threshold_por_ativo</t>
-        </is>
-      </c>
-      <c r="CM5" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="CN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ5" t="n">
-        <v>0.5599</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>0.5599</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CT5" t="inlineStr">
-        <is>
-          <t>vetado_esperanca_historica</t>
-        </is>
-      </c>
-      <c r="CU5" t="inlineStr"/>
-      <c r="CV5" t="inlineStr"/>
-      <c r="CW5" t="inlineStr"/>
-      <c r="CX5" t="inlineStr"/>
-      <c r="CY5" t="inlineStr"/>
-      <c r="CZ5" t="inlineStr">
-        <is>
-          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
-        </is>
-      </c>
-      <c r="DA5" t="inlineStr">
-        <is>
-          <t>vetada</t>
-        </is>
-      </c>
-      <c r="DB5" t="inlineStr"/>
-      <c r="DC5" t="inlineStr"/>
-      <c r="DD5" t="inlineStr"/>
-      <c r="DE5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2554,7 +2197,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JHSF3</t>
+          <t>ITSA4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2563,61 +2206,61 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46211</v>
+        <v>46221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Compra CALL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>naked_45</t>
+          <t>spread_45_15</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H2" t="n">
-        <v>10.35</v>
+        <v>13.61</v>
       </c>
       <c r="I2" t="n">
-        <v>11.05</v>
+        <v>13.52</v>
       </c>
       <c r="J2" t="n">
-        <v>6.76</v>
+        <v>-0.66</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.5</v>
+        <v>-0.257</v>
       </c>
       <c r="L2" t="n">
-        <v>0.49</v>
+        <v>0.425</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.32</v>
+        <v>-0.255</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.352</v>
+        <v>0.094</v>
       </c>
       <c r="P2" t="n">
-        <v>0.021</v>
+        <v>0.0039</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>razao=0.35 &lt; 0.6 | M=-0.50 — ativo foi contra, tese falhou</t>
+          <t>razao=0.09 &lt; 0.6 | M=-0.26 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SBFG3</t>
+          <t>JHSF3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2626,7 +2269,7 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46228</v>
+        <v>46211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2639,22 +2282,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>9.359999999999999</v>
+        <v>10.35</v>
       </c>
       <c r="I3" t="n">
-        <v>9.65</v>
+        <v>10.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>2.42</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.102</v>
+        <v>-0.022</v>
       </c>
       <c r="L3" t="n">
         <v>0.49</v>
@@ -2666,14 +2309,14 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.221</v>
+        <v>0.241</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0139</v>
+        <v>-0.0159</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>razao=0.22 &lt; 0.6 | M=-0.10 — ativo foi contra, tese falhou</t>
+          <t>razao=0.24 &lt; 0.6 | M=-0.02 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
@@ -2702,22 +2345,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
         <v>73.15000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>75.69</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>3.47</v>
+        <v>3.01</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.258</v>
+        <v>-0.209</v>
       </c>
       <c r="L4" t="n">
         <v>0.425</v>
@@ -2729,14 +2372,14 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.47</v>
+        <v>0.485</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0214</v>
+        <v>0.0212</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>razao=0.47 &lt; 0.6 | M=-0.26 — ativo foi contra, tese falhou</t>
+          <t>razao=0.48 &lt; 0.6 | M=-0.21 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
@@ -2765,10 +2408,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H5" t="n">
         <v>7.94</v>
@@ -2780,7 +2423,7 @@
         <v>2.77</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.007</v>
+        <v>-0.02</v>
       </c>
       <c r="L5" t="n">
         <v>0.49</v>
@@ -2792,21 +2435,21 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.578</v>
+        <v>0.357</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.0458</v>
+        <v>-0.0271</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>razao=0.58 &lt; 0.6 | M=-0.01 — ativo foi contra, tese falhou</t>
+          <t>razao=0.36 &lt; 0.6 | M=-0.02 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ITSA4</t>
+          <t>SBFG3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2815,54 +2458,54 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Compra CALL</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>spread_45_15</t>
+          <t>naked_45</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H6" t="n">
-        <v>13.61</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>13.76</v>
+        <v>9.32</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1</v>
+        <v>-0.43</v>
       </c>
       <c r="K6" t="n">
-        <v>0.006</v>
+        <v>0.247</v>
       </c>
       <c r="L6" t="n">
-        <v>0.425</v>
+        <v>0.49</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.255</v>
+        <v>-0.243</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.38</v>
+        <v>0.213</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0155</v>
+        <v>-0.0139</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>razao=0.38 &lt; 0.6 | M=0.01 — movimento OK, modelo ruidoso</t>
+          <t>razao=0.21 &lt; 0.6 | M=0.25 — movimento OK, modelo ruidoso</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2534,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H7" t="n">
         <v>18.77</v>
       </c>
       <c r="I7" t="n">
-        <v>18.77</v>
+        <v>18.42</v>
       </c>
       <c r="J7" t="n">
-        <v>-0</v>
+        <v>-1.86</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.175</v>
+        <v>-0.458</v>
       </c>
       <c r="L7" t="n">
         <v>0.49</v>
@@ -2918,14 +2561,14 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.442</v>
+        <v>0.649</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0547</v>
+        <v>0.026</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>M=-0.17 | razao=1.44 | 0/20d</t>
+          <t>M=-0.46 | razao=0.65 | 1/20d</t>
         </is>
       </c>
     </row>
@@ -2954,41 +2597,41 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H8" t="n">
         <v>0.79</v>
       </c>
       <c r="I8" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="J8" t="n">
-        <v>-0</v>
+        <v>-2.53</v>
       </c>
       <c r="K8" t="n">
-        <v>0.237</v>
+        <v>0.382</v>
       </c>
       <c r="L8" t="n">
         <v>0.49</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.253</v>
+        <v>-0.108</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.94</v>
+        <v>1.978</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2139</v>
+        <v>-0.2086</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>M=0.24 | razao=1.94 | 0/20d</t>
+          <t>M=0.38 | razao=1.98 | 1/20d</t>
         </is>
       </c>
     </row>
@@ -3017,41 +2660,41 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H9" t="n">
         <v>20.7</v>
       </c>
       <c r="I9" t="n">
-        <v>21.32</v>
+        <v>20.68</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>-0.1</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.08799999999999999</v>
+        <v>0.215</v>
       </c>
       <c r="L9" t="n">
         <v>0.49</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.32</v>
+        <v>-0.275</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.659</v>
+        <v>0.928</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.0419</v>
+        <v>-0.0603</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>M=-0.09 | razao=0.66 | 2/20d</t>
+          <t>M=0.22 | razao=0.93 | 3/20d</t>
         </is>
       </c>
     </row>
@@ -3080,41 +2723,41 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H10" t="n">
         <v>11.4</v>
       </c>
       <c r="I10" t="n">
-        <v>11.38</v>
+        <v>11.15</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.18</v>
+        <v>-2.19</v>
       </c>
       <c r="K10" t="n">
-        <v>0.229</v>
+        <v>0.468</v>
       </c>
       <c r="L10" t="n">
         <v>0.49</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.261</v>
+        <v>-0.022</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.578</v>
+        <v>1.928</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.0856</v>
+        <v>-0.1023</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>M=0.23 | razao=1.58 | 2/20d</t>
+          <t>M=0.47 | razao=1.93 | 3/20d</t>
         </is>
       </c>
     </row>
@@ -3143,41 +2786,41 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H11" t="n">
         <v>44.64</v>
       </c>
       <c r="I11" t="n">
-        <v>46.42</v>
+        <v>47.54</v>
       </c>
       <c r="J11" t="n">
-        <v>3.99</v>
+        <v>6.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.334</v>
+        <v>0.614</v>
       </c>
       <c r="L11" t="n">
         <v>0.751</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.181</v>
+        <v>-0.137</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.949</v>
+        <v>1.29</v>
       </c>
       <c r="P11" t="n">
-        <v>0.052</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>M=0.33 | razao=0.95 | 8/20d</t>
+          <t>M=0.61 | razao=1.29 | 9/20d</t>
         </is>
       </c>
     </row>
@@ -3206,22 +2849,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H12" t="n">
         <v>5.27</v>
       </c>
       <c r="I12" t="n">
-        <v>5.38</v>
+        <v>5.33</v>
       </c>
       <c r="J12" t="n">
-        <v>2.09</v>
+        <v>1.14</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.033</v>
+        <v>0.074</v>
       </c>
       <c r="L12" t="n">
         <v>0.49</v>
@@ -3233,14 +2876,14 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.749</v>
+        <v>0.709</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.0401</v>
+        <v>-0.0365</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>M=-0.03 | razao=0.75 | 1/20d</t>
+          <t>M=0.07 | razao=0.71 | 2/20d</t>
         </is>
       </c>
     </row>
@@ -3255,7 +2898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3368,7 +3011,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>GOAU4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3377,10 +3020,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3076</v>
+        <v>0.3362</v>
       </c>
       <c r="D2" t="n">
-        <v>1.106818</v>
+        <v>1.128108</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3388,7 +3031,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.2444</v>
+        <v>0.1909</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -3442,17 +3085,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[Empírico] Call delta~45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.328 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>[Empírico] Call delta~45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.259 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>0.0136</v>
+        <v>0.0158</v>
       </c>
       <c r="S2" t="n">
-        <v>21.6</v>
+        <v>25.1</v>
       </c>
       <c r="T2" t="n">
-        <v>23.9</v>
+        <v>28.3</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -3472,10 +3115,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2112</v>
+        <v>0.1881</v>
       </c>
       <c r="D3" t="n">
-        <v>1.154009</v>
+        <v>1.181753</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3483,7 +3126,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.6526999999999999</v>
+        <v>0.6643</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -3537,17 +3180,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.827 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.840 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0.0395</v>
+        <v>0.0378</v>
       </c>
       <c r="S3" t="n">
-        <v>62.7</v>
+        <v>60</v>
       </c>
       <c r="T3" t="n">
-        <v>72.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -3567,10 +3210,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.2226</v>
+        <v>0.1902</v>
       </c>
       <c r="D4" t="n">
-        <v>1.159549</v>
+        <v>1.17222</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -3604,78 +3247,15 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0.011</v>
+        <v>0.0106</v>
       </c>
       <c r="S4" t="n">
-        <v>17.5</v>
+        <v>16.8</v>
       </c>
       <c r="T4" t="n">
-        <v>20.2</v>
+        <v>19.7</v>
       </c>
       <c r="U4" t="inlineStr">
-        <is>
-          <t>Se IV_mercado &lt; vol_anualizada_pct → opção barata (compra favorável)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>USIM5</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Alerta CALL (VETADA)</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.2293</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.143976</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>forte</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>-0.0577</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>vetada</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>VETADA — esperança histórica insuficiente</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>0.0233</v>
-      </c>
-      <c r="S5" t="n">
-        <v>37</v>
-      </c>
-      <c r="T5" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="U5" t="inlineStr">
         <is>
           <t>Se IV_mercado &lt; vol_anualizada_pct → opção barata (compra favorável)</t>
         </is>
@@ -4239,7 +3819,7 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4272,7 +3852,7 @@
         <v>56</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1228</v>
+        <v>0.1225</v>
       </c>
       <c r="L2" t="n">
         <v>0.2321</v>
@@ -4290,13 +3870,13 @@
         <v>-0.0182</v>
       </c>
       <c r="Q2" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R2" t="n">
         <v>0.032</v>
       </c>
       <c r="S2" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="T2" t="n">
         <v>-0.0922</v>
@@ -4341,13 +3921,13 @@
         <v>-0.153</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0168</v>
+        <v>0.0169</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.4329</v>
+        <v>0.4353</v>
       </c>
       <c r="AH2" t="n">
-        <v>41.21</v>
+        <v>42</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -4356,13 +3936,13 @@
         <v>-0.0113</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.046003</v>
+        <v>0.077108</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.937612</v>
+        <v>0.915731</v>
       </c>
       <c r="AM2" t="n">
-        <v>-6.24</v>
+        <v>-8.43</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -4392,10 +3972,10 @@
         <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.047003</v>
+        <v>0.04714</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.9787</v>
+        <v>1.6357</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -4547,7 +4127,7 @@
         <v>0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.5202</v>
+        <v>0.5854</v>
       </c>
       <c r="CQ2" t="n">
         <v>0</v>
@@ -4576,7 +4156,7 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -4609,7 +4189,7 @@
         <v>43</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0945</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="L3" t="n">
         <v>0.6977</v>
@@ -4627,13 +4207,13 @@
         <v>-0.026</v>
       </c>
       <c r="Q3" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R3" t="n">
         <v>0.0979</v>
       </c>
       <c r="S3" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="T3" t="n">
         <v>0.322</v>
@@ -4674,13 +4254,13 @@
         <v>0.219</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0208</v>
+        <v>0.0199</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0873</v>
+        <v>0.0646</v>
       </c>
       <c r="AH3" t="n">
-        <v>42.47</v>
+        <v>42.57</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -4689,13 +4269,13 @@
         <v>0.0304</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.108787</v>
+        <v>0.07413699999999999</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.220294</v>
+        <v>1.256801</v>
       </c>
       <c r="AM3" t="n">
-        <v>22.03</v>
+        <v>25.68</v>
       </c>
       <c r="AN3" t="n">
         <v>1</v>
@@ -4725,10 +4305,10 @@
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.058038</v>
+        <v>0.055484</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.8744</v>
+        <v>1.3362</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
@@ -4876,7 +4456,7 @@
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.6329</v>
+        <v>0.5837</v>
       </c>
       <c r="CQ3" t="n">
         <v>0</v>
@@ -4905,7 +4485,7 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4919,7 +4499,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -4950,19 +4530,19 @@
         <v>0.3388</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0393</v>
+        <v>0.0392</v>
       </c>
       <c r="P4" t="n">
         <v>0.2067</v>
       </c>
       <c r="Q4" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3142</v>
+        <v>0.3141</v>
       </c>
       <c r="S4" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="T4" t="n">
         <v>0.1725</v>
@@ -5003,13 +4583,13 @@
         <v>0.3812</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0128</v>
+        <v>0.0135</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3559</v>
+        <v>0.4116</v>
       </c>
       <c r="AH4" t="n">
-        <v>42.86</v>
+        <v>42.05</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -5018,13 +4598,13 @@
         <v>0.0011</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.009955</v>
+        <v>-0.007856999999999999</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.033993</v>
+        <v>1.044836</v>
       </c>
       <c r="AM4" t="n">
-        <v>3.4</v>
+        <v>4.48</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
@@ -5054,10 +4634,10 @@
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.035586</v>
+        <v>0.037658</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.2798</v>
+        <v>0.2086</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
@@ -5209,7 +4789,7 @@
         <v>1</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.4753</v>
+        <v>0.457</v>
       </c>
       <c r="CQ4" t="n">
         <v>0</v>
@@ -5238,7 +4818,7 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5271,7 +4851,7 @@
         <v>165</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3618</v>
+        <v>0.3611</v>
       </c>
       <c r="L5" t="n">
         <v>0.7091</v>
@@ -5286,16 +4866,16 @@
         <v>0.7824</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2858</v>
+        <v>0.2827</v>
       </c>
       <c r="Q5" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R5" t="n">
-        <v>0.577</v>
+        <v>0.5619</v>
       </c>
       <c r="S5" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="T5" t="n">
         <v>0.642</v>
@@ -5336,28 +4916,28 @@
         <v>0.2479</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0163</v>
+        <v>0.0156</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.5397</v>
+        <v>0.5063</v>
       </c>
       <c r="AH5" t="n">
-        <v>75.69</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.2323</v>
+        <v>0.2318</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.02137</v>
+        <v>0.021164</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.936615</v>
+        <v>0.977406</v>
       </c>
       <c r="AM5" t="n">
-        <v>-6.34</v>
+        <v>-2.26</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
@@ -5369,7 +4949,7 @@
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
         <v>1.03</v>
@@ -5387,10 +4967,10 @@
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.045506</v>
+        <v>0.043663</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.4696</v>
+        <v>0.4847</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
@@ -5542,7 +5122,7 @@
         <v>1</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.4402</v>
+        <v>0.4484</v>
       </c>
       <c r="CQ5" t="n">
         <v>0</v>
@@ -5571,7 +5151,7 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -5580,7 +5160,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5589,29 +5169,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4079</v>
+        <v>0.4092</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6774</v>
+        <v>0.6791</v>
       </c>
       <c r="M6" t="n">
         <v>0.3564</v>
@@ -5620,25 +5196,25 @@
         <v>0.8997000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1563</v>
+        <v>0.1543</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1232</v>
+        <v>0.1215</v>
       </c>
       <c r="Q6" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1624</v>
+        <v>0.1619</v>
       </c>
       <c r="S6" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2444</v>
+        <v>0.2421</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0489</v>
+        <v>0.0488</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -5652,49 +5228,49 @@
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
-        <v>0.3277</v>
+        <v>0.3261</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.024</v>
+        <v>1.0191</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.2434</v>
+        <v>0.2411</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.3277</v>
+        <v>0.3261</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0919</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.1455</v>
+        <v>0.1452</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0136</v>
+        <v>0.0143</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.3076</v>
+        <v>0.3628</v>
       </c>
       <c r="AH6" t="n">
-        <v>18.77</v>
+        <v>18.42</v>
       </c>
       <c r="AI6" t="n">
-        <v>19.36</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0997</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.054728</v>
+        <v>0.025985</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.106818</v>
+        <v>1.072745</v>
       </c>
       <c r="AM6" t="n">
-        <v>10.68</v>
+        <v>7.27</v>
       </c>
       <c r="AN6" t="n">
         <v>1</v>
@@ -5721,13 +5297,13 @@
         <v>1</v>
       </c>
       <c r="AV6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.037963</v>
+        <v>0.040034</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.4416</v>
+        <v>0.6491</v>
       </c>
       <c r="AY6" t="n">
         <v>0</v>
@@ -5737,7 +5313,7 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -5879,71 +5455,27 @@
         <v>0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.5767</v>
+        <v>0.4864</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.5767</v>
-      </c>
-      <c r="CR6" t="inlineStr">
-        <is>
-          <t>Call delta~45 naked (quase ATM, ~0.9σ, 20d)</t>
-        </is>
-      </c>
-      <c r="CS6" t="inlineStr">
-        <is>
-          <t>Call delta~50 naked (ATM, máximo gamma)</t>
-        </is>
-      </c>
-      <c r="CT6" t="inlineStr">
-        <is>
-          <t>Call delta~40 naked (ligeiramente mais OTM)</t>
-        </is>
-      </c>
-      <c r="CU6" t="inlineStr">
-        <is>
-          <t>OTM extremo (&lt;delta~20) sem vol prevista muito forte</t>
-        </is>
-      </c>
-      <c r="CV6" t="inlineStr">
-        <is>
-          <t>~0.45</t>
-        </is>
-      </c>
-      <c r="CW6" t="inlineStr">
-        <is>
-          <t>naked_30: esp=+0.243 | spread_35_20: esp=+0.070 | spread_45_25: esp=+0.092 | spread_45_15: esp=+0.145</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="CR6" t="inlineStr"/>
+      <c r="CS6" t="inlineStr"/>
+      <c r="CT6" t="inlineStr"/>
+      <c r="CU6" t="inlineStr"/>
+      <c r="CV6" t="inlineStr"/>
+      <c r="CW6" t="inlineStr"/>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>[Empírico] Call delta~45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.328 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
-        </is>
-      </c>
-      <c r="CY6" t="inlineStr">
-        <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="CZ6" t="inlineStr">
-        <is>
-          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.053%/dia | carry 20 pregões: 1.06%]</t>
-        </is>
-      </c>
-      <c r="DA6" t="inlineStr">
-        <is>
-          <t>100% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="DB6" t="inlineStr">
-        <is>
-          <t>50% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="DC6" t="inlineStr">
-        <is>
-          <t>Edge forte — aguardar dobrar o prêmio. Stop 50%.</t>
-        </is>
-      </c>
+          <t>Ticker neutro — sem sinal operacional</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr"/>
+      <c r="CZ6" t="inlineStr"/>
+      <c r="DA6" t="inlineStr"/>
+      <c r="DB6" t="inlineStr"/>
+      <c r="DC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5952,7 +5484,7 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -5978,14 +5510,14 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>59</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1294</v>
+        <v>0.1291</v>
       </c>
       <c r="L7" t="n">
         <v>0.3729</v>
@@ -6003,13 +5535,13 @@
         <v>0.0303</v>
       </c>
       <c r="Q7" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R7" t="n">
         <v>0.0619</v>
       </c>
       <c r="S7" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="T7" t="n">
         <v>0.0128</v>
@@ -6054,13 +5586,13 @@
         <v>-0.0296</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0214</v>
+        <v>0.0229</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.3742</v>
+        <v>0.4335</v>
       </c>
       <c r="AH7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -6069,13 +5601,13 @@
         <v>0.0017</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.046078</v>
+        <v>0.036817</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.9989440000000001</v>
+        <v>0.968639</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.11</v>
+        <v>-3.14</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
@@ -6105,10 +5637,10 @@
         <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.059601</v>
+        <v>0.063774</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.7731</v>
+        <v>0.5773</v>
       </c>
       <c r="AY7" t="n">
         <v>0</v>
@@ -6118,12 +5650,12 @@
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>compressao</t>
         </is>
       </c>
       <c r="BC7" t="n">
@@ -6260,7 +5792,7 @@
         <v>0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.4649</v>
+        <v>0.4335</v>
       </c>
       <c r="CQ7" t="n">
         <v>0</v>
@@ -6289,7 +5821,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -6319,13 +5851,13 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K8" t="n">
-        <v>0.318</v>
+        <v>0.3195</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4483</v>
+        <v>0.4452</v>
       </c>
       <c r="M8" t="n">
         <v>0.3046</v>
@@ -6340,19 +5872,19 @@
         <v>-0.0526</v>
       </c>
       <c r="Q8" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R8" t="n">
         <v>-0.0404</v>
       </c>
       <c r="S8" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1491</v>
+        <v>0.1469</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0485</v>
+        <v>0.0484</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -6366,49 +5898,49 @@
       </c>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="n">
-        <v>0.1647</v>
+        <v>0.1614</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5148</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.1481</v>
+        <v>0.1459</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1647</v>
+        <v>0.1614</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0205</v>
+        <v>0.0195</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0074</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0402</v>
+        <v>0.0382</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0318</v>
+        <v>0.0306</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.2758</v>
+        <v>0.2238</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.83</v>
+        <v>4.77</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0474</v>
+        <v>0.0469</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0005330000000000001</v>
+        <v>0.005413</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.12038</v>
+        <v>1.117832</v>
       </c>
       <c r="AM8" t="n">
-        <v>12.04</v>
+        <v>11.78</v>
       </c>
       <c r="AN8" t="n">
         <v>1</v>
@@ -6438,10 +5970,10 @@
         <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.08860700000000001</v>
+        <v>0.085285</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.006</v>
+        <v>0.0635</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
@@ -6593,7 +6125,7 @@
         <v>1</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.4426</v>
+        <v>0.4588</v>
       </c>
       <c r="CQ8" t="n">
         <v>0</v>
@@ -6622,7 +6154,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -6655,7 +6187,7 @@
         <v>73</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1601</v>
+        <v>0.1597</v>
       </c>
       <c r="L9" t="n">
         <v>0.4384</v>
@@ -6673,13 +6205,13 @@
         <v>0.0086</v>
       </c>
       <c r="Q9" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R9" t="n">
         <v>0.0305</v>
       </c>
       <c r="S9" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="T9" t="n">
         <v>0.1722</v>
@@ -6720,28 +6252,28 @@
         <v>-0.0119</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0196</v>
+        <v>0.0198</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.4801</v>
+        <v>0.4888</v>
       </c>
       <c r="AH9" t="n">
-        <v>46.42</v>
+        <v>47.54</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.051975</v>
+        <v>0.07137</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.954115</v>
+        <v>0.936724</v>
       </c>
       <c r="AM9" t="n">
-        <v>-4.59</v>
+        <v>-6.33</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
@@ -6771,10 +6303,10 @@
         <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.054778</v>
+        <v>0.055302</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.9488</v>
+        <v>1.2905</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
@@ -6926,7 +6458,7 @@
         <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.5139</v>
+        <v>0.5464</v>
       </c>
       <c r="CQ9" t="n">
         <v>0</v>
@@ -6955,7 +6487,7 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -6988,7 +6520,7 @@
         <v>16</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0351</v>
+        <v>0.035</v>
       </c>
       <c r="L10" t="n">
         <v>0.6875</v>
@@ -7003,16 +6535,16 @@
         <v>0.2055</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1619</v>
+        <v>0.1543</v>
       </c>
       <c r="Q10" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2615</v>
+        <v>0.2591</v>
       </c>
       <c r="S10" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="T10" t="n">
         <v>0.2173</v>
@@ -7053,13 +6585,13 @@
         <v>0.2834</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0146</v>
+        <v>0.015</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.4609</v>
+        <v>0.4858</v>
       </c>
       <c r="AH10" t="n">
-        <v>13.76</v>
+        <v>13.52</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -7068,13 +6600,13 @@
         <v>0.0076</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.015451</v>
+        <v>0.003912</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.986306</v>
+        <v>0.97655</v>
       </c>
       <c r="AM10" t="n">
-        <v>-1.37</v>
+        <v>-2.34</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
@@ -7104,10 +6636,10 @@
         <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.040708</v>
+        <v>0.041743</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.3796</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="AY10" t="n">
         <v>0</v>
@@ -7122,7 +6654,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>compressao</t>
         </is>
       </c>
       <c r="BC10" t="n">
@@ -7259,7 +6791,7 @@
         <v>1</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.4417</v>
+        <v>0.4081</v>
       </c>
       <c r="CQ10" t="n">
         <v>0</v>
@@ -7288,7 +6820,7 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -7321,7 +6853,7 @@
         <v>125</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2741</v>
+        <v>0.2735</v>
       </c>
       <c r="L11" t="n">
         <v>0.672</v>
@@ -7339,13 +6871,13 @@
         <v>0.169</v>
       </c>
       <c r="Q11" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R11" t="n">
         <v>0.249</v>
       </c>
       <c r="S11" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T11" t="n">
         <v>0.2378</v>
@@ -7389,25 +6921,25 @@
         <v>0.0165</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.3948</v>
+        <v>0.3931</v>
       </c>
       <c r="AH11" t="n">
-        <v>25.14</v>
+        <v>24.9</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.16075</v>
+        <v>0.149313</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.863</v>
+        <v>0.8941519999999999</v>
       </c>
       <c r="AM11" t="n">
-        <v>-13.7</v>
+        <v>-10.58</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
@@ -7437,10 +6969,10 @@
         <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.045989</v>
+        <v>0.045913</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.4954</v>
+        <v>3.2521</v>
       </c>
       <c r="AY11" t="n">
         <v>1</v>
@@ -7592,7 +7124,7 @@
         <v>0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.5735</v>
       </c>
       <c r="CQ11" t="n">
         <v>0</v>
@@ -7621,7 +7153,7 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -7630,7 +7162,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -7639,26 +7171,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>57</v>
       </c>
       <c r="K12" t="n">
-        <v>0.125</v>
+        <v>0.1247</v>
       </c>
       <c r="L12" t="n">
         <v>0.5263</v>
@@ -7673,10 +7201,10 @@
         <v>-0.18</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.0184</v>
+        <v>-0.0221</v>
       </c>
       <c r="Q12" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R12" t="n">
         <v>-0.0692</v>
@@ -7727,37 +7255,37 @@
         <v>-0.0561</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0233</v>
+        <v>0.0266</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.2293</v>
+        <v>0.3588</v>
       </c>
       <c r="AH12" t="n">
-        <v>8.69</v>
+        <v>8.26</v>
       </c>
       <c r="AI12" t="n">
-        <v>9.16</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
         <v>-0.0072</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.06879</v>
+        <v>0.016831</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.143976</v>
+        <v>1.12131</v>
       </c>
       <c r="AM12" t="n">
-        <v>14.4</v>
+        <v>12.13</v>
       </c>
       <c r="AN12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
         <v>0</v>
@@ -7775,13 +7303,13 @@
         <v>1</v>
       </c>
       <c r="AV12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.06489499999999999</v>
+        <v>0.074368</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.06</v>
+        <v>0.2263</v>
       </c>
       <c r="AY12" t="n">
         <v>0</v>
@@ -7791,12 +7319,12 @@
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>expansao</t>
+          <t>neutro_zona_cinza</t>
         </is>
       </c>
       <c r="BC12" t="n">
@@ -7933,35 +7461,23 @@
         <v>0</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.5599</v>
+        <v>0.4507</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.5599</v>
-      </c>
-      <c r="CR12" t="inlineStr">
-        <is>
-          <t>Sem estrutura com edge positivo — não operar</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="CR12" t="inlineStr"/>
       <c r="CS12" t="inlineStr"/>
       <c r="CT12" t="inlineStr"/>
-      <c r="CU12" t="inlineStr">
-        <is>
-          <t>Qualquer compra: nenhuma estrutura supera o ruído amostral</t>
-        </is>
-      </c>
+      <c r="CU12" t="inlineStr"/>
       <c r="CV12" t="inlineStr"/>
       <c r="CW12" t="inlineStr"/>
       <c r="CX12" t="inlineStr">
         <is>
-          <t>Nenhuma estrutura tem esperança acima do ruído amostral (E−SE&gt;0). Não operar.</t>
-        </is>
-      </c>
-      <c r="CY12" t="inlineStr">
-        <is>
-          <t>baixa</t>
-        </is>
-      </c>
+          <t>Ticker neutro — sem sinal operacional</t>
+        </is>
+      </c>
+      <c r="CY12" t="inlineStr"/>
       <c r="CZ12" t="inlineStr"/>
       <c r="DA12" t="inlineStr"/>
       <c r="DB12" t="inlineStr"/>
@@ -7974,7 +7490,7 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -8007,7 +7523,7 @@
         <v>19</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0417</v>
+        <v>0.0416</v>
       </c>
       <c r="L13" t="n">
         <v>0.5789</v>
@@ -8025,13 +7541,13 @@
         <v>-0.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R13" t="n">
         <v>-0.1221</v>
       </c>
       <c r="S13" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="T13" t="n">
         <v>-0.092</v>
@@ -8076,13 +7592,13 @@
         <v>-0.008</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0219</v>
+        <v>0.0233</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.3186</v>
+        <v>0.3883</v>
       </c>
       <c r="AH13" t="n">
-        <v>13.9</v>
+        <v>13.41</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -8091,13 +7607,13 @@
         <v>-0.0038</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.009472</v>
+        <v>-0.022653</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.993719</v>
+        <v>0.998602</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0.63</v>
+        <v>-0.14</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
@@ -8127,10 +7643,10 @@
         <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.061018</v>
+        <v>0.06496300000000001</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.1552</v>
+        <v>0.3487</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
@@ -8278,7 +7794,7 @@
         <v>0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.4797</v>
+        <v>0.4851</v>
       </c>
       <c r="CQ13" t="n">
         <v>0</v>
@@ -8307,7 +7823,7 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -8340,7 +7856,7 @@
         <v>106</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2325</v>
+        <v>0.2319</v>
       </c>
       <c r="L14" t="n">
         <v>0.5755</v>
@@ -8355,10 +7871,10 @@
         <v>0.0302</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0323</v>
+        <v>0.0385</v>
       </c>
       <c r="Q14" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R14" t="n">
         <v>0.0675</v>
@@ -8374,24 +7890,20 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>nenhuma</t>
+          <t>naked_45</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>spread_35_20,spread_45_15,spread_45_25</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>risco</t>
-        </is>
-      </c>
+          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
       <c r="Y14" t="n">
-        <v>-0.18</v>
+        <v>0.0584</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>0.1826</v>
       </c>
       <c r="AA14" t="n">
         <v>0.0333</v>
@@ -8409,13 +7921,13 @@
         <v>0.0311</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0149</v>
+        <v>0.0142</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.6227</v>
+        <v>0.5749</v>
       </c>
       <c r="AH14" t="n">
-        <v>41.21</v>
+        <v>41.18</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -8424,13 +7936,13 @@
         <v>0.008</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.01836</v>
+        <v>0.022285</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.888196</v>
+        <v>0.982198</v>
       </c>
       <c r="AM14" t="n">
-        <v>-11.18</v>
+        <v>-1.78</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
@@ -8460,10 +7972,10 @@
         <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.041529</v>
+        <v>0.039755</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.4421</v>
+        <v>0.5606</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
@@ -8478,7 +7990,7 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>compressao</t>
+          <t>neutro_zona_cinza</t>
         </is>
       </c>
       <c r="BC14" t="n">
@@ -8611,7 +8123,7 @@
         <v>0</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.2851</v>
+        <v>0.3065</v>
       </c>
       <c r="CQ14" t="n">
         <v>0</v>
@@ -8640,7 +8152,7 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -8673,7 +8185,7 @@
         <v>121</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2654</v>
+        <v>0.2648</v>
       </c>
       <c r="L15" t="n">
         <v>0.7685999999999999</v>
@@ -8688,16 +8200,16 @@
         <v>1.1777</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3561</v>
+        <v>0.3468</v>
       </c>
       <c r="Q15" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5649</v>
       </c>
       <c r="S15" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="T15" t="n">
         <v>1.4438</v>
@@ -8738,28 +8250,28 @@
         <v>0.3815</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.0385</v>
+        <v>0.0369</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.225</v>
+        <v>0.2104</v>
       </c>
       <c r="AH15" t="n">
-        <v>10.6</v>
+        <v>10.49</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.3831</v>
+        <v>0.3823</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0.069524</v>
+        <v>-0.07579</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.01504</v>
+        <v>1.038626</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.5</v>
+        <v>3.86</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
@@ -8789,10 +8301,10 @@
         <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.10735</v>
+        <v>0.1029</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.6476</v>
+        <v>0.7365</v>
       </c>
       <c r="AY15" t="n">
         <v>0</v>
@@ -8944,7 +8456,7 @@
         <v>1</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.5003</v>
+        <v>0.5122</v>
       </c>
       <c r="CQ15" t="n">
         <v>0</v>
@@ -8973,7 +8485,7 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -9006,7 +8518,7 @@
         <v>68</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1491</v>
+        <v>0.1488</v>
       </c>
       <c r="L16" t="n">
         <v>0.2794</v>
@@ -9024,13 +8536,13 @@
         <v>0.09379999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R16" t="n">
         <v>0.1492</v>
       </c>
       <c r="S16" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="T16" t="n">
         <v>-0.0988</v>
@@ -9075,13 +8587,13 @@
         <v>-0.1003</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0287</v>
+        <v>0.0278</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.3282</v>
+        <v>0.2967</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.66</v>
+        <v>4.57</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -9090,22 +8602,22 @@
         <v>-0.0147</v>
       </c>
       <c r="AK16" t="n">
-        <v>-0.020941</v>
+        <v>-0.021621</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.074508</v>
+        <v>1.082745</v>
       </c>
       <c r="AM16" t="n">
-        <v>7.45</v>
+        <v>8.27</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ16" t="n">
         <v>0</v>
@@ -9126,10 +8638,10 @@
         <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.07996499999999999</v>
+        <v>0.07756200000000001</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.2619</v>
+        <v>0.2788</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
@@ -9144,7 +8656,7 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>expansao</t>
         </is>
       </c>
       <c r="BC16" t="n">
@@ -9281,7 +8793,7 @@
         <v>1</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.4622</v>
+        <v>0.4701</v>
       </c>
       <c r="CQ16" t="n">
         <v>0</v>
@@ -9310,7 +8822,7 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -9343,7 +8855,7 @@
         <v>29</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0636</v>
+        <v>0.0635</v>
       </c>
       <c r="L17" t="n">
         <v>0.3793</v>
@@ -9361,13 +8873,13 @@
         <v>-0.1523</v>
       </c>
       <c r="Q17" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R17" t="n">
         <v>0.0461</v>
       </c>
       <c r="S17" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="T17" t="n">
         <v>0.1048</v>
@@ -9412,28 +8924,28 @@
         <v>-0.0331</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0132</v>
+        <v>0.0128</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.0916</v>
+        <v>0.0806</v>
       </c>
       <c r="AH17" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.0067</v>
+        <v>0.0066</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.023942</v>
+        <v>0.025491</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.227257</v>
+        <v>1.231796</v>
       </c>
       <c r="AM17" t="n">
-        <v>22.73</v>
+        <v>23.18</v>
       </c>
       <c r="AN17" t="n">
         <v>1</v>
@@ -9463,10 +8975,10 @@
         <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.036733</v>
+        <v>0.035599</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.6518</v>
+        <v>0.716</v>
       </c>
       <c r="AY17" t="n">
         <v>0</v>
@@ -9618,7 +9130,7 @@
         <v>0</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.4961</v>
+        <v>0.5047</v>
       </c>
       <c r="CQ17" t="n">
         <v>0</v>
@@ -9647,7 +9159,7 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -9673,7 +9185,7 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -9698,13 +9210,13 @@
         <v>-0.0225</v>
       </c>
       <c r="Q18" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R18" t="n">
         <v>-0.1272</v>
       </c>
       <c r="S18" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="T18" t="n">
         <v>-0.18</v>
@@ -9733,13 +9245,13 @@
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="n">
-        <v>0.0335</v>
+        <v>0.0395</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.458</v>
+        <v>0.6129</v>
       </c>
       <c r="AH18" t="n">
-        <v>5.64</v>
+        <v>5.23</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -9748,13 +9260,13 @@
         <v>-0</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.176382</v>
+        <v>0.083161</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.935353</v>
+        <v>0.884536</v>
       </c>
       <c r="AM18" t="n">
-        <v>-6.46</v>
+        <v>-11.55</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
@@ -9766,7 +9278,7 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR18" t="n">
         <v>1.084286</v>
@@ -9784,10 +9296,10 @@
         <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.093523</v>
+        <v>0.110177</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.886</v>
+        <v>0.7548</v>
       </c>
       <c r="AY18" t="n">
         <v>0</v>
@@ -9797,7 +9309,7 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
@@ -9935,7 +9447,7 @@
         <v>1</v>
       </c>
       <c r="CP18" t="n">
-        <v>0.6001</v>
+        <v>0.456</v>
       </c>
       <c r="CQ18" t="n">
         <v>0</v>
@@ -9964,7 +9476,7 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -9990,17 +9502,17 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1404</v>
+        <v>0.1422</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8594000000000001</v>
+        <v>0.8462</v>
       </c>
       <c r="M19" t="n">
         <v>0.4615</v>
@@ -10015,19 +9527,19 @@
         <v>-0.0107</v>
       </c>
       <c r="Q19" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R19" t="n">
         <v>0.2725</v>
       </c>
       <c r="S19" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9987</v>
+        <v>0.9806</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2458</v>
+        <v>0.2446</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -10041,49 +9553,49 @@
       </c>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="n">
-        <v>1.1201</v>
+        <v>1.098</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.5004</v>
+        <v>3.4312</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.9977</v>
+        <v>0.9796</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.1201</v>
+        <v>1.098</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.1105</v>
+        <v>0.1068</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.1427</v>
+        <v>0.1375</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.2198</v>
+        <v>0.2125</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.0129</v>
+        <v>0.0131</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.5011</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="AH19" t="n">
-        <v>39.8</v>
+        <v>39.13</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.1402</v>
+        <v>0.1395</v>
       </c>
       <c r="AK19" t="n">
-        <v>-0.011146</v>
+        <v>-0.033642</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.92816</v>
+        <v>0.846634</v>
       </c>
       <c r="AM19" t="n">
-        <v>-7.18</v>
+        <v>-15.34</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
@@ -10113,10 +9625,10 @@
         <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.035928</v>
+        <v>0.03643</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.3102</v>
+        <v>0.9235</v>
       </c>
       <c r="AY19" t="n">
         <v>0</v>
@@ -10126,7 +9638,7 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
@@ -10264,7 +9776,7 @@
         <v>0</v>
       </c>
       <c r="CP19" t="n">
-        <v>0.3936</v>
+        <v>0.4524</v>
       </c>
       <c r="CQ19" t="n">
         <v>0</v>
@@ -10293,7 +9805,7 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -10319,14 +9831,14 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>69</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1513</v>
+        <v>0.151</v>
       </c>
       <c r="L20" t="n">
         <v>0.6667</v>
@@ -10344,13 +9856,13 @@
         <v>-0.0055</v>
       </c>
       <c r="Q20" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R20" t="n">
         <v>-0.0351</v>
       </c>
       <c r="S20" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="T20" t="n">
         <v>0.1439</v>
@@ -10391,28 +9903,28 @@
         <v>0.1336</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.0228</v>
+        <v>0.0233</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.2425</v>
+        <v>0.2522</v>
       </c>
       <c r="AH20" t="n">
-        <v>21.32</v>
+        <v>20.68</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.0218</v>
+        <v>0.0217</v>
       </c>
       <c r="AK20" t="n">
-        <v>-0.041948</v>
+        <v>-0.060325</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.98128</v>
+        <v>0.9791069999999999</v>
       </c>
       <c r="AM20" t="n">
-        <v>-1.87</v>
+        <v>-2.09</v>
       </c>
       <c r="AN20" t="n">
         <v>0</v>
@@ -10442,10 +9954,10 @@
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.06361600000000001</v>
+        <v>0.06498900000000001</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.6594</v>
+        <v>0.9282</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
@@ -10455,12 +9967,12 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>compressao</t>
         </is>
       </c>
       <c r="BC20" t="n">
@@ -10597,7 +10109,7 @@
         <v>0</v>
       </c>
       <c r="CP20" t="n">
-        <v>0.4687</v>
+        <v>0.4936</v>
       </c>
       <c r="CQ20" t="n">
         <v>0</v>
@@ -10626,7 +10138,7 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -10652,14 +10164,14 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>51</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1118</v>
+        <v>0.1116</v>
       </c>
       <c r="L21" t="n">
         <v>0.6863</v>
@@ -10677,13 +10189,13 @@
         <v>-0.0915</v>
       </c>
       <c r="Q21" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R21" t="n">
         <v>-0.0484</v>
       </c>
       <c r="S21" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="T21" t="n">
         <v>0.102</v>
@@ -10728,13 +10240,13 @@
         <v>0.0421</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.0184</v>
+        <v>0.0188</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.0984</v>
+        <v>0.1084</v>
       </c>
       <c r="AH21" t="n">
-        <v>18.2</v>
+        <v>17.79</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -10743,13 +10255,13 @@
         <v>0.0114</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.039287</v>
+        <v>0.026684</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.079021</v>
+        <v>1.08536</v>
       </c>
       <c r="AM21" t="n">
-        <v>7.9</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="AN21" t="n">
         <v>0</v>
@@ -10779,10 +10291,10 @@
         <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.051296</v>
+        <v>0.052567</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.7659</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
@@ -10792,7 +10304,7 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
@@ -10934,7 +10446,7 @@
         <v>1</v>
       </c>
       <c r="CP21" t="n">
-        <v>0.5308</v>
+        <v>0.5029</v>
       </c>
       <c r="CQ21" t="n">
         <v>0</v>
@@ -10963,7 +10475,7 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -10977,7 +10489,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -10996,7 +10508,7 @@
         <v>72</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1579</v>
+        <v>0.1575</v>
       </c>
       <c r="L22" t="n">
         <v>0.5972</v>
@@ -11014,13 +10526,13 @@
         <v>0.2538</v>
       </c>
       <c r="Q22" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R22" t="n">
         <v>0.5024999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="T22" t="n">
         <v>0.3343</v>
@@ -11061,37 +10573,37 @@
         <v>0.1537</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.0214</v>
+        <v>0.0237</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.2749</v>
+        <v>0.3606</v>
       </c>
       <c r="AH22" t="n">
-        <v>11.05</v>
+        <v>10.6</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.0528</v>
+        <v>0.0527</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.020977</v>
+        <v>-0.015945</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.109268</v>
+        <v>1.159498</v>
       </c>
       <c r="AM22" t="n">
-        <v>10.93</v>
+        <v>15.95</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ22" t="n">
         <v>0</v>
@@ -11112,10 +10624,10 @@
         <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.059668</v>
+        <v>0.066188</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.3516</v>
+        <v>0.2409</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
@@ -11130,7 +10642,7 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>expansao</t>
         </is>
       </c>
       <c r="BC22" t="n">
@@ -11263,7 +10775,7 @@
         <v>0</v>
       </c>
       <c r="CP22" t="n">
-        <v>0.4186</v>
+        <v>0.3904</v>
       </c>
       <c r="CQ22" t="n">
         <v>0</v>
@@ -11292,7 +10804,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -11318,17 +10830,17 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2917</v>
+        <v>0.2932</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4361</v>
+        <v>0.4328</v>
       </c>
       <c r="M23" t="n">
         <v>0.1714</v>
@@ -11343,19 +10855,19 @@
         <v>0.0219</v>
       </c>
       <c r="Q23" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R23" t="n">
         <v>0.1334</v>
       </c>
       <c r="S23" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0583</v>
+        <v>-0.0592</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0234</v>
+        <v>0.0233</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -11379,43 +10891,43 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>-0.0593</v>
+        <v>-0.0602</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.0822</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.0257</v>
+        <v>-0.0265</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.0447</v>
+        <v>-0.0458</v>
       </c>
       <c r="AE23" t="n">
-        <v>-0.053</v>
+        <v>-0.0545</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.0176</v>
+        <v>0.0216</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.366</v>
+        <v>0.5353</v>
       </c>
       <c r="AH23" t="n">
-        <v>28.27</v>
+        <v>26.87</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-0.017</v>
+        <v>-0.0174</v>
       </c>
       <c r="AK23" t="n">
-        <v>-0.032839</v>
+        <v>-0.066098</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.025918</v>
+        <v>0.971697</v>
       </c>
       <c r="AM23" t="n">
-        <v>2.59</v>
+        <v>-2.83</v>
       </c>
       <c r="AN23" t="n">
         <v>0</v>
@@ -11445,10 +10957,10 @@
         <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.049065</v>
+        <v>0.06021</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.6693</v>
+        <v>1.0978</v>
       </c>
       <c r="AY23" t="n">
         <v>0</v>
@@ -11458,12 +10970,12 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>compressao</t>
         </is>
       </c>
       <c r="BC23" t="n">
@@ -11600,7 +11112,7 @@
         <v>1</v>
       </c>
       <c r="CP23" t="n">
-        <v>0.5014</v>
+        <v>0.5104</v>
       </c>
       <c r="CQ23" t="n">
         <v>0</v>
@@ -11629,7 +11141,7 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -11638,7 +11150,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11647,52 +11159,56 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
+          <t>alerta_executor_nivel_B</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>114</v>
       </c>
       <c r="K24" t="n">
-        <v>0.25</v>
+        <v>0.2495</v>
       </c>
       <c r="L24" t="n">
         <v>0.7193000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3826</v>
+        <v>0.3793</v>
       </c>
       <c r="N24" t="n">
         <v>0.7677</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3162</v>
+        <v>0.3161</v>
       </c>
       <c r="P24" t="n">
         <v>0.0615</v>
       </c>
       <c r="Q24" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R24" t="n">
         <v>0.3719</v>
       </c>
       <c r="S24" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="T24" t="n">
         <v>0.1909</v>
       </c>
       <c r="U24" t="n">
-        <v>0.052</v>
+        <v>0.0518</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -11727,34 +11243,34 @@
         <v>0.1303</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.0157</v>
+        <v>0.0158</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.3306</v>
+        <v>0.3362</v>
       </c>
       <c r="AH24" t="n">
-        <v>10.89</v>
+        <v>10.77</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>11.17</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.0477</v>
+        <v>0.0476</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.131477</v>
+        <v>0.118415</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.099024</v>
+        <v>1.128108</v>
       </c>
       <c r="AM24" t="n">
-        <v>9.9</v>
+        <v>12.81</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP24" t="n">
         <v>0</v>
@@ -11775,13 +11291,13 @@
         <v>1</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.04386</v>
+        <v>0.044087</v>
       </c>
       <c r="AX24" t="n">
-        <v>2.9977</v>
+        <v>2.686</v>
       </c>
       <c r="AY24" t="n">
         <v>0</v>
@@ -11933,27 +11449,71 @@
         <v>0</v>
       </c>
       <c r="CP24" t="n">
-        <v>0.5934</v>
+        <v>0.5923</v>
       </c>
       <c r="CQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR24" t="inlineStr"/>
-      <c r="CS24" t="inlineStr"/>
-      <c r="CT24" t="inlineStr"/>
-      <c r="CU24" t="inlineStr"/>
-      <c r="CV24" t="inlineStr"/>
-      <c r="CW24" t="inlineStr"/>
+        <v>0.5923</v>
+      </c>
+      <c r="CR24" t="inlineStr">
+        <is>
+          <t>Call delta~45 naked (quase ATM, ~0.9σ, 20d)</t>
+        </is>
+      </c>
+      <c r="CS24" t="inlineStr">
+        <is>
+          <t>Call delta~50 naked (ATM, máximo gamma)</t>
+        </is>
+      </c>
+      <c r="CT24" t="inlineStr">
+        <is>
+          <t>Call delta~40 naked (ligeiramente mais OTM)</t>
+        </is>
+      </c>
+      <c r="CU24" t="inlineStr">
+        <is>
+          <t>OTM extremo (&lt;delta~20) sem vol prevista muito forte</t>
+        </is>
+      </c>
+      <c r="CV24" t="inlineStr">
+        <is>
+          <t>~0.45</t>
+        </is>
+      </c>
+      <c r="CW24" t="inlineStr">
+        <is>
+          <t>naked_30: esp=+0.190 | spread_35_20: esp=+0.067 | spread_45_25: esp=+0.078 | spread_45_15: esp=+0.130</t>
+        </is>
+      </c>
       <c r="CX24" t="inlineStr">
         <is>
-          <t>Ticker neutro — sem sinal operacional</t>
-        </is>
-      </c>
-      <c r="CY24" t="inlineStr"/>
-      <c r="CZ24" t="inlineStr"/>
-      <c r="DA24" t="inlineStr"/>
-      <c r="DB24" t="inlineStr"/>
-      <c r="DC24" t="inlineStr"/>
+          <t>[Empírico] Call delta~45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.259 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+        </is>
+      </c>
+      <c r="CY24" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="CZ24" t="inlineStr">
+        <is>
+          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.053%/dia | carry 20 pregões: 1.06%]</t>
+        </is>
+      </c>
+      <c r="DA24" t="inlineStr">
+        <is>
+          <t>100% do prêmio pago</t>
+        </is>
+      </c>
+      <c r="DB24" t="inlineStr">
+        <is>
+          <t>50% do prêmio pago</t>
+        </is>
+      </c>
+      <c r="DC24" t="inlineStr">
+        <is>
+          <t>Edge forte — aguardar dobrar o prêmio. Stop 50%.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11962,7 +11522,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -11995,7 +11555,7 @@
         <v>54</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1184</v>
+        <v>0.1182</v>
       </c>
       <c r="L25" t="n">
         <v>0.6296</v>
@@ -12010,10 +11570,10 @@
         <v>0.1656</v>
       </c>
       <c r="P25" t="n">
-        <v>0.0281</v>
+        <v>0.0321</v>
       </c>
       <c r="Q25" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R25" t="n">
         <v>0.1041</v>
@@ -12064,13 +11624,13 @@
         <v>0.0626</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.0195</v>
+        <v>0.0193</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.6661</v>
+        <v>0.6473</v>
       </c>
       <c r="AH25" t="n">
-        <v>30.01</v>
+        <v>29.41</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -12079,13 +11639,13 @@
         <v>0.0061</v>
       </c>
       <c r="AK25" t="n">
-        <v>-0.022007</v>
+        <v>-0.01272</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.936501</v>
+        <v>0.940334</v>
       </c>
       <c r="AM25" t="n">
-        <v>-6.35</v>
+        <v>-5.97</v>
       </c>
       <c r="AN25" t="n">
         <v>0</v>
@@ -12115,10 +11675,10 @@
         <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.054544</v>
+        <v>0.053734</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.4035</v>
+        <v>0.2367</v>
       </c>
       <c r="AY25" t="n">
         <v>0</v>
@@ -12270,7 +11830,7 @@
         <v>1</v>
       </c>
       <c r="CP25" t="n">
-        <v>0.4037</v>
+        <v>0.3908</v>
       </c>
       <c r="CQ25" t="n">
         <v>0</v>
@@ -12299,7 +11859,7 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -12332,7 +11892,7 @@
         <v>148</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3246</v>
+        <v>0.3239</v>
       </c>
       <c r="L26" t="n">
         <v>0.6351</v>
@@ -12347,16 +11907,16 @@
         <v>0.3573</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1636</v>
+        <v>0.1531</v>
       </c>
       <c r="Q26" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R26" t="n">
-        <v>0.5039</v>
+        <v>0.495</v>
       </c>
       <c r="S26" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="T26" t="n">
         <v>0.5133</v>
@@ -12397,28 +11957,28 @@
         <v>0.139</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.0171</v>
+        <v>0.0163</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.5642</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="AH26" t="n">
-        <v>21.76</v>
+        <v>21.69</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.1666</v>
+        <v>0.1662</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.019371</v>
+        <v>0.022114</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.911649</v>
+        <v>0.971884</v>
       </c>
       <c r="AM26" t="n">
-        <v>-8.84</v>
+        <v>-2.81</v>
       </c>
       <c r="AN26" t="n">
         <v>0</v>
@@ -12430,7 +11990,7 @@
         <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
         <v>1.03</v>
@@ -12448,10 +12008,10 @@
         <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.047596</v>
+        <v>0.045573</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.407</v>
+        <v>0.4852</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
@@ -12603,7 +12163,7 @@
         <v>0</v>
       </c>
       <c r="CP26" t="n">
-        <v>0.3961</v>
+        <v>0.4112</v>
       </c>
       <c r="CQ26" t="n">
         <v>0</v>
@@ -12632,7 +12192,7 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -12665,7 +12225,7 @@
         <v>25</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0548</v>
+        <v>0.0547</v>
       </c>
       <c r="L27" t="n">
         <v>0.08</v>
@@ -12680,16 +12240,16 @@
         <v>0.0129</v>
       </c>
       <c r="P27" t="n">
-        <v>0.1016</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="Q27" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R27" t="n">
-        <v>0.4355</v>
+        <v>0.4302</v>
       </c>
       <c r="S27" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="T27" t="n">
         <v>-0.1646</v>
@@ -12734,13 +12294,13 @@
         <v>-0.222</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.0388</v>
+        <v>0.0379</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.244</v>
+        <v>0.2305</v>
       </c>
       <c r="AH27" t="n">
-        <v>5.96</v>
+        <v>6.08</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -12749,13 +12309,13 @@
         <v>-0.008999999999999999</v>
       </c>
       <c r="AK27" t="n">
-        <v>-0.056514</v>
+        <v>-0.020195</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.009343</v>
+        <v>1.004003</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.93</v>
+        <v>0.4</v>
       </c>
       <c r="AN27" t="n">
         <v>0</v>
@@ -12785,10 +12345,10 @@
         <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.108328</v>
+        <v>0.105708</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.191</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -12936,7 +12496,7 @@
         <v>0</v>
       </c>
       <c r="CP27" t="n">
-        <v>0.474</v>
+        <v>0.4437</v>
       </c>
       <c r="CQ27" t="n">
         <v>0</v>
@@ -12965,7 +12525,7 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -12998,7 +12558,7 @@
         <v>80</v>
       </c>
       <c r="K28" t="n">
-        <v>0.1754</v>
+        <v>0.1751</v>
       </c>
       <c r="L28" t="n">
         <v>0.5625</v>
@@ -13016,13 +12576,13 @@
         <v>0.0025</v>
       </c>
       <c r="Q28" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R28" t="n">
         <v>0.0442</v>
       </c>
       <c r="S28" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="T28" t="n">
         <v>0.09379999999999999</v>
@@ -13067,28 +12627,28 @@
         <v>0.0243</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.0246</v>
+        <v>0.0266</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.5407</v>
+        <v>0.6172</v>
       </c>
       <c r="AH28" t="n">
-        <v>11.64</v>
+        <v>11.07</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.0165</v>
+        <v>0.0164</v>
       </c>
       <c r="AK28" t="n">
-        <v>-0.095135</v>
+        <v>-0.115684</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.069328</v>
+        <v>1.085961</v>
       </c>
       <c r="AM28" t="n">
-        <v>6.93</v>
+        <v>8.6</v>
       </c>
       <c r="AN28" t="n">
         <v>0</v>
@@ -13118,10 +12678,10 @@
         <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.068534</v>
+        <v>0.07413400000000001</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.3882</v>
+        <v>1.5605</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
@@ -13269,7 +12829,7 @@
         <v>0</v>
       </c>
       <c r="CP28" t="n">
-        <v>0.479</v>
+        <v>0.481</v>
       </c>
       <c r="CQ28" t="n">
         <v>0</v>
@@ -13298,7 +12858,7 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -13324,7 +12884,7 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -13349,13 +12909,13 @@
         <v>-0.18</v>
       </c>
       <c r="Q29" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R29" t="n">
         <v>-0.0736</v>
       </c>
       <c r="S29" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="T29" t="n">
         <v>-0.1591</v>
@@ -13400,13 +12960,13 @@
         <v>-0.06850000000000001</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.0208</v>
+        <v>0.0204</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.2217</v>
+        <v>0.2094</v>
       </c>
       <c r="AH29" t="n">
-        <v>3.41</v>
+        <v>3.45</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -13415,13 +12975,13 @@
         <v>-0.0028</v>
       </c>
       <c r="AK29" t="n">
-        <v>-0.03875</v>
+        <v>-0.015583</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.110396</v>
+        <v>1.107826</v>
       </c>
       <c r="AM29" t="n">
-        <v>11.04</v>
+        <v>10.78</v>
       </c>
       <c r="AN29" t="n">
         <v>0</v>
@@ -13451,10 +13011,10 @@
         <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.05806</v>
+        <v>0.056928</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.6674</v>
+        <v>0.2737</v>
       </c>
       <c r="AY29" t="n">
         <v>0</v>
@@ -13464,7 +13024,7 @@
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
@@ -13602,7 +13162,7 @@
         <v>0</v>
       </c>
       <c r="CP29" t="n">
-        <v>0.5082</v>
+        <v>0.4713</v>
       </c>
       <c r="CQ29" t="n">
         <v>0</v>
@@ -13631,7 +13191,7 @@
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -13664,7 +13224,7 @@
         <v>124</v>
       </c>
       <c r="K30" t="n">
-        <v>0.2719</v>
+        <v>0.2713</v>
       </c>
       <c r="L30" t="n">
         <v>0.6613</v>
@@ -13682,13 +13242,13 @@
         <v>0.0013</v>
       </c>
       <c r="Q30" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R30" t="n">
         <v>0.0726</v>
       </c>
       <c r="S30" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="T30" t="n">
         <v>0.1501</v>
@@ -13729,28 +13289,28 @@
         <v>0.1138</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.0192</v>
+        <v>0.0185</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.3422</v>
+        <v>0.3169</v>
       </c>
       <c r="AH30" t="n">
-        <v>5.38</v>
+        <v>5.33</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.0408</v>
+        <v>0.0407</v>
       </c>
       <c r="AK30" t="n">
-        <v>-0.040058</v>
+        <v>-0.036524</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.091862</v>
+        <v>1.102425</v>
       </c>
       <c r="AM30" t="n">
-        <v>9.19</v>
+        <v>10.24</v>
       </c>
       <c r="AN30" t="n">
         <v>1</v>
@@ -13780,10 +13340,10 @@
         <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.053517</v>
+        <v>0.051526</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.7088</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
@@ -13935,7 +13495,7 @@
         <v>1</v>
       </c>
       <c r="CP30" t="n">
-        <v>0.5165</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="CQ30" t="n">
         <v>0</v>
@@ -13964,7 +13524,7 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -13997,7 +13557,7 @@
         <v>139</v>
       </c>
       <c r="K31" t="n">
-        <v>0.3048</v>
+        <v>0.3042</v>
       </c>
       <c r="L31" t="n">
         <v>0.7122000000000001</v>
@@ -14015,13 +13575,13 @@
         <v>0.0574</v>
       </c>
       <c r="Q31" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R31" t="n">
         <v>0.0502</v>
       </c>
       <c r="S31" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="T31" t="n">
         <v>0.1482</v>
@@ -14066,28 +13626,28 @@
         <v>0.0533</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.0178</v>
+        <v>0.0181</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.471</v>
+        <v>0.4831</v>
       </c>
       <c r="AH31" t="n">
-        <v>14.93</v>
+        <v>14.63</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.0452</v>
+        <v>0.0451</v>
       </c>
       <c r="AK31" t="n">
-        <v>-0.00214</v>
+        <v>-0.011322</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.132573</v>
+        <v>1.120376</v>
       </c>
       <c r="AM31" t="n">
-        <v>13.26</v>
+        <v>12.04</v>
       </c>
       <c r="AN31" t="n">
         <v>1</v>
@@ -14117,10 +13677,10 @@
         <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.049803</v>
+        <v>0.050394</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.043</v>
+        <v>0.2247</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
@@ -14268,7 +13828,7 @@
         <v>0</v>
       </c>
       <c r="CP31" t="n">
-        <v>0.3389</v>
+        <v>0.3546</v>
       </c>
       <c r="CQ31" t="n">
         <v>0</v>
@@ -14297,7 +13857,7 @@
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -14334,37 +13894,37 @@
         <v>43</v>
       </c>
       <c r="K32" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.0941</v>
       </c>
       <c r="L32" t="n">
         <v>0.6512</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0702</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>0.2666</v>
+        <v>0.2667</v>
       </c>
       <c r="O32" t="n">
         <v>-0.18</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.058</v>
+        <v>-0.0437</v>
       </c>
       <c r="Q32" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.0722</v>
+        <v>-0.0717</v>
       </c>
       <c r="S32" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="T32" t="n">
         <v>-0.1354</v>
       </c>
       <c r="U32" t="n">
-        <v>0.0178</v>
+        <v>0.0177</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -14403,28 +13963,28 @@
         <v>-0.1207</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.011</v>
+        <v>0.0106</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.2226</v>
+        <v>0.1902</v>
       </c>
       <c r="AH32" t="n">
         <v>18.04</v>
       </c>
       <c r="AI32" t="n">
-        <v>18.5</v>
+        <v>18.48</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-0.0128</v>
+        <v>-0.0127</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.053343</v>
+        <v>0.042047</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.159549</v>
+        <v>1.17222</v>
       </c>
       <c r="AM32" t="n">
-        <v>15.95</v>
+        <v>17.22</v>
       </c>
       <c r="AN32" t="n">
         <v>1</v>
@@ -14454,10 +14014,10 @@
         <v>1</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.030743</v>
+        <v>0.029493</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.7351</v>
+        <v>1.4256</v>
       </c>
       <c r="AY32" t="n">
         <v>0</v>
@@ -14605,10 +14165,10 @@
         <v>0</v>
       </c>
       <c r="CP32" t="n">
-        <v>0.5809</v>
+        <v>0.5564</v>
       </c>
       <c r="CQ32" t="n">
-        <v>0.5809</v>
+        <v>0.5564</v>
       </c>
       <c r="CR32" t="inlineStr">
         <is>
@@ -14646,7 +14206,7 @@
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -14697,13 +14257,13 @@
         <v>0.1278</v>
       </c>
       <c r="Q33" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R33" t="n">
         <v>0.2698</v>
       </c>
       <c r="S33" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="T33" t="n">
         <v>0.4839</v>
@@ -14744,13 +14304,13 @@
         <v>0.0979</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.0164</v>
+        <v>0.0173</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.3747</v>
+        <v>0.417</v>
       </c>
       <c r="AH33" t="n">
-        <v>27.14</v>
+        <v>26.46</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -14759,13 +14319,13 @@
         <v>0.0106</v>
       </c>
       <c r="AK33" t="n">
-        <v>-0.01547</v>
+        <v>-0.022997</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.921199</v>
+        <v>0.874369</v>
       </c>
       <c r="AM33" t="n">
-        <v>-7.88</v>
+        <v>-12.56</v>
       </c>
       <c r="AN33" t="n">
         <v>0</v>
@@ -14795,10 +14355,10 @@
         <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.045719</v>
+        <v>0.048179</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.3384</v>
+        <v>0.4773</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
@@ -14950,7 +14510,7 @@
         <v>1</v>
       </c>
       <c r="CP33" t="n">
-        <v>0.4228</v>
+        <v>0.4282</v>
       </c>
       <c r="CQ33" t="n">
         <v>0</v>
@@ -14979,7 +14539,7 @@
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -15009,44 +14569,44 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K34" t="n">
-        <v>0.0482</v>
+        <v>0.0503</v>
       </c>
       <c r="L34" t="n">
-        <v>0.3182</v>
+        <v>0.3478</v>
       </c>
       <c r="M34" t="n">
-        <v>0.2917</v>
+        <v>0.3333</v>
       </c>
       <c r="N34" t="n">
-        <v>2.1867</v>
+        <v>2.2054</v>
       </c>
       <c r="O34" t="n">
-        <v>2.2783</v>
+        <v>2.3074</v>
       </c>
       <c r="P34" t="n">
-        <v>-0.1594</v>
+        <v>-0.1484</v>
       </c>
       <c r="Q34" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R34" t="n">
         <v>-0.18</v>
       </c>
       <c r="S34" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="T34" t="n">
-        <v>0.573</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="U34" t="n">
-        <v>0.2349</v>
+        <v>0.2414</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>naked_30</t>
+          <t>naked_45</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -15056,49 +14616,49 @@
       </c>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="n">
-        <v>0.572</v>
+        <v>0.6488</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.1604</v>
+        <v>2.0276</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.572</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.5603</v>
+        <v>0.6488</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.0177</v>
+        <v>0.0313</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.0208</v>
+        <v>-0.0045</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.0216</v>
+        <v>0.0474</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.0196</v>
+        <v>0.0195</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.4102</v>
+        <v>0.4054</v>
       </c>
       <c r="AH34" t="n">
-        <v>32.45</v>
+        <v>32.05</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.0276</v>
+        <v>0.0327</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.08622199999999999</v>
+        <v>0.07681</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.722166</v>
+        <v>0.700828</v>
       </c>
       <c r="AM34" t="n">
-        <v>-27.78</v>
+        <v>-29.92</v>
       </c>
       <c r="AN34" t="n">
         <v>0</v>
@@ -15128,10 +14688,10 @@
         <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.054716</v>
+        <v>0.054447</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.5758</v>
+        <v>1.4107</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
@@ -15279,7 +14839,7 @@
         <v>0</v>
       </c>
       <c r="CP34" t="n">
-        <v>0.5382</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="CQ34" t="n">
         <v>0</v>
@@ -15308,7 +14868,7 @@
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -15341,7 +14901,7 @@
         <v>35</v>
       </c>
       <c r="K35" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0766</v>
       </c>
       <c r="L35" t="n">
         <v>0.3143</v>
@@ -15356,16 +14916,16 @@
         <v>-0.098</v>
       </c>
       <c r="P35" t="n">
-        <v>0.0039</v>
+        <v>0.0008</v>
       </c>
       <c r="Q35" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R35" t="n">
-        <v>0.0472</v>
+        <v>0.0456</v>
       </c>
       <c r="S35" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="T35" t="n">
         <v>-0.1032</v>
@@ -15413,10 +14973,10 @@
         <v>0.0221</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.4073</v>
+        <v>0.406</v>
       </c>
       <c r="AH35" t="n">
-        <v>21.44</v>
+        <v>21.03</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -15425,13 +14985,13 @@
         <v>-0.007900000000000001</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.013666</v>
+        <v>0.018183</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.92705</v>
+        <v>0.931104</v>
       </c>
       <c r="AM35" t="n">
-        <v>-7.3</v>
+        <v>-6.89</v>
       </c>
       <c r="AN35" t="n">
         <v>0</v>
@@ -15461,10 +15021,10 @@
         <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.061748</v>
+        <v>0.061669</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.2213</v>
+        <v>0.2949</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
@@ -15612,7 +15172,7 @@
         <v>0</v>
       </c>
       <c r="CP35" t="n">
-        <v>0.4074</v>
+        <v>0.415</v>
       </c>
       <c r="CQ35" t="n">
         <v>0</v>
@@ -15641,7 +15201,7 @@
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -15671,13 +15231,13 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K36" t="n">
-        <v>0.1009</v>
+        <v>0.1028</v>
       </c>
       <c r="L36" t="n">
-        <v>0.4348</v>
+        <v>0.4255</v>
       </c>
       <c r="M36" t="n">
         <v>0.36</v>
@@ -15692,19 +15252,19 @@
         <v>0.1003</v>
       </c>
       <c r="Q36" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R36" t="n">
         <v>0.1797</v>
       </c>
       <c r="S36" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="T36" t="n">
-        <v>0.1176</v>
+        <v>0.1112</v>
       </c>
       <c r="U36" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.0638</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -15718,49 +15278,49 @@
       </c>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="n">
-        <v>0.1488</v>
+        <v>0.1388</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.465</v>
+        <v>0.4339</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.1166</v>
+        <v>0.1102</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.1488</v>
+        <v>0.1388</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.0542</v>
+        <v>0.0503</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.0359</v>
+        <v>0.031</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.0906</v>
+        <v>0.0833</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.0165</v>
+        <v>0.0197</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.4128</v>
+        <v>0.5712</v>
       </c>
       <c r="AH36" t="n">
-        <v>28.79</v>
+        <v>27.6</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.0119</v>
+        <v>0.0114</v>
       </c>
       <c r="AK36" t="n">
-        <v>-0.003356</v>
+        <v>-0.030675</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.907406</v>
+        <v>0.904258</v>
       </c>
       <c r="AM36" t="n">
-        <v>-9.26</v>
+        <v>-9.57</v>
       </c>
       <c r="AN36" t="n">
         <v>0</v>
@@ -15790,10 +15350,10 @@
         <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.045945</v>
+        <v>0.055107</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.0731</v>
+        <v>0.5566</v>
       </c>
       <c r="AY36" t="n">
         <v>0</v>
@@ -15945,7 +15505,7 @@
         <v>0</v>
       </c>
       <c r="CP36" t="n">
-        <v>0.3755</v>
+        <v>0.3921</v>
       </c>
       <c r="CQ36" t="n">
         <v>0</v>
@@ -15974,7 +15534,7 @@
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -15988,7 +15548,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -16007,7 +15567,7 @@
         <v>22</v>
       </c>
       <c r="K37" t="n">
-        <v>0.0482</v>
+        <v>0.0481</v>
       </c>
       <c r="L37" t="n">
         <v>0.8636</v>
@@ -16022,16 +15582,16 @@
         <v>0.4577</v>
       </c>
       <c r="P37" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.5826</v>
       </c>
       <c r="Q37" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R37" t="n">
-        <v>0.8572</v>
+        <v>0.8485</v>
       </c>
       <c r="S37" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="T37" t="n">
         <v>0.3336</v>
@@ -16072,13 +15632,13 @@
         <v>0.1978</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.02</v>
+        <v>0.0243</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.2847</v>
+        <v>0.4007</v>
       </c>
       <c r="AH37" t="n">
-        <v>64.39</v>
+        <v>61.21</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -16087,13 +15647,13 @@
         <v>0.0161</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.02272</v>
+        <v>-0.010101</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.6495649999999999</v>
+        <v>0.643989</v>
       </c>
       <c r="AM37" t="n">
-        <v>-35.04</v>
+        <v>-35.6</v>
       </c>
       <c r="AN37" t="n">
         <v>0</v>
@@ -16123,10 +15683,10 @@
         <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.055902</v>
+        <v>0.067881</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.4064</v>
+        <v>0.1488</v>
       </c>
       <c r="AY37" t="n">
         <v>0</v>
@@ -16274,7 +15834,7 @@
         <v>0</v>
       </c>
       <c r="CP37" t="n">
-        <v>0.4613</v>
+        <v>0.4123</v>
       </c>
       <c r="CQ37" t="n">
         <v>0</v>
@@ -16303,7 +15863,7 @@
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -16336,7 +15896,7 @@
         <v>77</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1689</v>
+        <v>0.1685</v>
       </c>
       <c r="L38" t="n">
         <v>0.5974</v>
@@ -16354,13 +15914,13 @@
         <v>-0.168</v>
       </c>
       <c r="Q38" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R38" t="n">
         <v>-0.0547</v>
       </c>
       <c r="S38" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="T38" t="n">
         <v>0.0565</v>
@@ -16401,10 +15961,10 @@
         <v>0.027</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.0284</v>
+        <v>0.0271</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.281</v>
+        <v>0.2376</v>
       </c>
       <c r="AH38" t="n">
         <v>8.16</v>
@@ -16416,13 +15976,13 @@
         <v>0.0095</v>
       </c>
       <c r="AK38" t="n">
-        <v>-0.045788</v>
+        <v>-0.027055</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.107654</v>
+        <v>1.113619</v>
       </c>
       <c r="AM38" t="n">
-        <v>10.77</v>
+        <v>11.36</v>
       </c>
       <c r="AN38" t="n">
         <v>1</v>
@@ -16452,10 +16012,10 @@
         <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.079197</v>
+        <v>0.07568999999999999</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.5782</v>
+        <v>0.3574</v>
       </c>
       <c r="AY38" t="n">
         <v>0</v>
@@ -16607,7 +16167,7 @@
         <v>1</v>
       </c>
       <c r="CP38" t="n">
-        <v>0.4952</v>
+        <v>0.4818</v>
       </c>
       <c r="CQ38" t="n">
         <v>0</v>
@@ -16636,7 +16196,7 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -16666,13 +16226,13 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1623</v>
+        <v>0.1641</v>
       </c>
       <c r="L39" t="n">
-        <v>0.4865</v>
+        <v>0.48</v>
       </c>
       <c r="M39" t="n">
         <v>0.3165</v>
@@ -16687,19 +16247,19 @@
         <v>-0.0022</v>
       </c>
       <c r="Q39" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R39" t="n">
         <v>0.0395</v>
       </c>
       <c r="S39" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="T39" t="n">
-        <v>0.1547</v>
+        <v>0.1503</v>
       </c>
       <c r="U39" t="n">
-        <v>0.0625</v>
+        <v>0.0622</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -16713,49 +16273,49 @@
       </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="n">
-        <v>0.1645</v>
+        <v>0.1582</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.5142</v>
+        <v>0.4943</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.1537</v>
+        <v>0.1493</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.1645</v>
+        <v>0.1582</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.0233</v>
+        <v>0.0213</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.0041</v>
+        <v>0.0015</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.0451</v>
+        <v>0.0412</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.0155</v>
+        <v>0.0149</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.5545</v>
+        <v>0.5162</v>
       </c>
       <c r="AH39" t="n">
-        <v>13.16</v>
+        <v>13.07</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.0251</v>
+        <v>0.0247</v>
       </c>
       <c r="AK39" t="n">
-        <v>-0.000254</v>
+        <v>-0.002998</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.127403</v>
+        <v>1.15442</v>
       </c>
       <c r="AM39" t="n">
-        <v>12.74</v>
+        <v>15.44</v>
       </c>
       <c r="AN39" t="n">
         <v>0</v>
@@ -16785,10 +16345,10 @@
         <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.043321</v>
+        <v>0.041508</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.0059</v>
+        <v>0.0722</v>
       </c>
       <c r="AY39" t="n">
         <v>0</v>
@@ -16940,7 +16500,7 @@
         <v>0</v>
       </c>
       <c r="CP39" t="n">
-        <v>0.3701</v>
+        <v>0.3844</v>
       </c>
       <c r="CQ39" t="n">
         <v>0</v>
@@ -16969,7 +16529,7 @@
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -16983,7 +16543,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -17002,7 +16562,7 @@
         <v>69</v>
       </c>
       <c r="K40" t="n">
-        <v>0.152</v>
+        <v>0.1516</v>
       </c>
       <c r="L40" t="n">
         <v>0.7826</v>
@@ -17020,13 +16580,13 @@
         <v>-0.1704</v>
       </c>
       <c r="Q40" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="R40" t="n">
         <v>-0.0815</v>
       </c>
       <c r="S40" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="T40" t="n">
         <v>0.07049999999999999</v>
@@ -17071,13 +16631,13 @@
         <v>-0.014</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.0253</v>
+        <v>0.0244</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.9053</v>
+        <v>0.8587</v>
       </c>
       <c r="AH40" t="n">
-        <v>26.84</v>
+        <v>26.46</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -17086,13 +16646,13 @@
         <v>0.0107</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.003778</v>
+        <v>-0.000534</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.871166</v>
+        <v>0.875564</v>
       </c>
       <c r="AM40" t="n">
-        <v>-12.88</v>
+        <v>-12.44</v>
       </c>
       <c r="AN40" t="n">
         <v>0</v>
@@ -17122,10 +16682,10 @@
         <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.07059</v>
+        <v>0.067994</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.0535</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="AY40" t="n">
         <v>0</v>
@@ -17273,7 +16833,7 @@
         <v>0</v>
       </c>
       <c r="CP40" t="n">
-        <v>0.3086</v>
+        <v>0.3134</v>
       </c>
       <c r="CQ40" t="n">
         <v>0</v>
@@ -17302,7 +16862,7 @@
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -17316,7 +16876,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -17353,13 +16913,13 @@
         <v>-0.1375</v>
       </c>
       <c r="Q41" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R41" t="n">
         <v>-0.1291</v>
       </c>
       <c r="S41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="T41" t="n">
         <v>0.1187</v>
@@ -17404,13 +16964,13 @@
         <v>-0.08119999999999999</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.0129</v>
+        <v>0.0164</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.1739</v>
+        <v>0.389</v>
       </c>
       <c r="AH41" t="n">
-        <v>14.69</v>
+        <v>14.15</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -17419,13 +16979,13 @@
         <v>0.0026</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.012667</v>
+        <v>-0.005681</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.084565</v>
+        <v>1.053327</v>
       </c>
       <c r="AM41" t="n">
-        <v>8.460000000000001</v>
+        <v>5.33</v>
       </c>
       <c r="AN41" t="n">
         <v>0</v>
@@ -17455,10 +17015,10 @@
         <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.035931</v>
+        <v>0.045642</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.3525</v>
+        <v>0.1245</v>
       </c>
       <c r="AY41" t="n">
         <v>0</v>
@@ -17610,7 +17170,7 @@
         <v>1</v>
       </c>
       <c r="CP41" t="n">
-        <v>0.5204</v>
+        <v>0.4546</v>
       </c>
       <c r="CQ41" t="n">
         <v>0</v>
@@ -17639,7 +17199,7 @@
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -17669,13 +17229,13 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K42" t="n">
-        <v>0.1732</v>
+        <v>0.1751</v>
       </c>
       <c r="L42" t="n">
-        <v>0.3797</v>
+        <v>0.3875</v>
       </c>
       <c r="M42" t="n">
         <v>0.1829</v>
@@ -17684,25 +17244,25 @@
         <v>0.9302</v>
       </c>
       <c r="O42" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.0347</v>
       </c>
       <c r="P42" t="n">
-        <v>-0.03</v>
+        <v>-0.0393</v>
       </c>
       <c r="Q42" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R42" t="n">
-        <v>-0.0211</v>
+        <v>-0.0247</v>
       </c>
       <c r="S42" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="T42" t="n">
-        <v>0.0345</v>
+        <v>0.0318</v>
       </c>
       <c r="U42" t="n">
-        <v>0.0653</v>
+        <v>0.065</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -17726,43 +17286,43 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.0335</v>
+        <v>0.0308</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.0032</v>
+        <v>-0.0008</v>
       </c>
       <c r="AC42" t="n">
-        <v>-0.0343</v>
+        <v>-0.0355</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.0549</v>
+        <v>-0.0566</v>
       </c>
       <c r="AE42" t="n">
-        <v>-0.064</v>
+        <v>-0.0664</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.0162</v>
+        <v>0.0173</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.4502</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="AH42" t="n">
-        <v>54.91</v>
+        <v>53.56</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.006</v>
+        <v>0.0056</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.015275</v>
+        <v>0.004044</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.018285</v>
+        <v>1.015294</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AN42" t="n">
         <v>0</v>
@@ -17792,10 +17352,10 @@
         <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.045194</v>
+        <v>0.048192</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.338</v>
+        <v>0.0839</v>
       </c>
       <c r="AY42" t="n">
         <v>0</v>
@@ -17947,7 +17507,7 @@
         <v>0</v>
       </c>
       <c r="CP42" t="n">
-        <v>0.4394</v>
+        <v>0.3999</v>
       </c>
       <c r="CQ42" t="n">
         <v>0</v>
@@ -17976,7 +17536,7 @@
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -18010,40 +17570,40 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K43" t="n">
-        <v>0.1031</v>
+        <v>0.105</v>
       </c>
       <c r="L43" t="n">
-        <v>0.8298</v>
+        <v>0.8333</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4426</v>
+        <v>0.4516</v>
       </c>
       <c r="N43" t="n">
-        <v>1.286</v>
+        <v>1.2835</v>
       </c>
       <c r="O43" t="n">
-        <v>0.7336</v>
+        <v>0.7368</v>
       </c>
       <c r="P43" t="n">
-        <v>-0.059</v>
+        <v>-0.0485</v>
       </c>
       <c r="Q43" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R43" t="n">
-        <v>0.0101</v>
+        <v>0.0118</v>
       </c>
       <c r="S43" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="T43" t="n">
-        <v>0.6526999999999999</v>
+        <v>0.6643</v>
       </c>
       <c r="U43" t="n">
-        <v>0.1187</v>
+        <v>0.117</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -18057,49 +17617,49 @@
       </c>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="n">
-        <v>0.8267</v>
+        <v>0.8399</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.5833</v>
+        <v>2.6248</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.6633</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.8267</v>
+        <v>0.8399</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.1626</v>
+        <v>0.166</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.2106</v>
+        <v>0.2136</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.3251</v>
+        <v>0.331</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.0395</v>
+        <v>0.0378</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.2112</v>
+        <v>0.1881</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.0673</v>
+        <v>0.0698</v>
       </c>
       <c r="AK43" t="n">
-        <v>-0.213894</v>
+        <v>-0.208582</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.154009</v>
+        <v>1.181753</v>
       </c>
       <c r="AM43" t="n">
-        <v>15.4</v>
+        <v>18.18</v>
       </c>
       <c r="AN43" t="n">
         <v>1</v>
@@ -18129,10 +17689,10 @@
         <v>-1</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.110244</v>
+        <v>0.105469</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.9402</v>
+        <v>1.9777</v>
       </c>
       <c r="AY43" t="n">
         <v>0</v>
@@ -18280,10 +17840,10 @@
         <v>1</v>
       </c>
       <c r="CP43" t="n">
-        <v>0.6287</v>
+        <v>0.6371</v>
       </c>
       <c r="CQ43" t="n">
-        <v>0.6287</v>
+        <v>0.6371</v>
       </c>
       <c r="CR43" t="inlineStr">
         <is>
@@ -18312,12 +17872,12 @@
       </c>
       <c r="CW43" t="inlineStr">
         <is>
-          <t>naked_30: esp=+0.652 | spread_35_20: esp=+0.163 | spread_45_25: esp=+0.211 | spread_45_15: esp=+0.325</t>
+          <t>naked_30: esp=+0.663 | spread_35_20: esp=+0.166 | spread_45_25: esp=+0.214 | spread_45_15: esp=+0.331</t>
         </is>
       </c>
       <c r="CX43" t="inlineStr">
         <is>
-          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.827 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.840 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
         </is>
       </c>
       <c r="CY43" t="inlineStr">
@@ -18353,7 +17913,7 @@
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -18386,7 +17946,7 @@
         <v>21</v>
       </c>
       <c r="K44" t="n">
-        <v>0.0461</v>
+        <v>0.046</v>
       </c>
       <c r="L44" t="n">
         <v>0.4762</v>
@@ -18401,16 +17961,16 @@
         <v>0.4407</v>
       </c>
       <c r="P44" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.0755</v>
       </c>
       <c r="Q44" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R44" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="S44" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="T44" t="n">
         <v>0.1812</v>
@@ -18451,13 +18011,13 @@
         <v>0.1186</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.0162</v>
+        <v>0.0168</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.2383</v>
+        <v>0.2724</v>
       </c>
       <c r="AH44" t="n">
-        <v>17.06</v>
+        <v>16.76</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -18466,13 +18026,13 @@
         <v>0.0083</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.047552</v>
+        <v>0.039666</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.090834</v>
+        <v>1.08893</v>
       </c>
       <c r="AM44" t="n">
-        <v>9.08</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AN44" t="n">
         <v>0</v>
@@ -18502,10 +18062,10 @@
         <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.045294</v>
+        <v>0.046957</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.0498</v>
+        <v>0.8447</v>
       </c>
       <c r="AY44" t="n">
         <v>0</v>
@@ -18657,7 +18217,7 @@
         <v>0</v>
       </c>
       <c r="CP44" t="n">
-        <v>0.5434</v>
+        <v>0.5161</v>
       </c>
       <c r="CQ44" t="n">
         <v>0</v>
@@ -18686,7 +18246,7 @@
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -18719,7 +18279,7 @@
         <v>41</v>
       </c>
       <c r="K45" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.0897</v>
       </c>
       <c r="L45" t="n">
         <v>0.5610000000000001</v>
@@ -18734,16 +18294,16 @@
         <v>0.1479</v>
       </c>
       <c r="P45" t="n">
-        <v>-0.1793</v>
+        <v>-0.1786</v>
       </c>
       <c r="Q45" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R45" t="n">
-        <v>0.013</v>
+        <v>0.0172</v>
       </c>
       <c r="S45" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="T45" t="n">
         <v>0.0654</v>
@@ -18784,13 +18344,13 @@
         <v>0.1134</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.0225</v>
+        <v>0.0234</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.1749</v>
+        <v>0.2227</v>
       </c>
       <c r="AH45" t="n">
-        <v>9.65</v>
+        <v>9.32</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -18799,13 +18359,13 @@
         <v>0.0059</v>
       </c>
       <c r="AK45" t="n">
-        <v>-0.013872</v>
+        <v>-0.013911</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.273217</v>
+        <v>1.242197</v>
       </c>
       <c r="AM45" t="n">
-        <v>27.32</v>
+        <v>24.22</v>
       </c>
       <c r="AN45" t="n">
         <v>0</v>
@@ -18835,10 +18395,10 @@
         <v>0</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.062663</v>
+        <v>0.06529799999999999</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.2214</v>
+        <v>0.213</v>
       </c>
       <c r="AY45" t="n">
         <v>0</v>
@@ -18986,7 +18546,7 @@
         <v>0</v>
       </c>
       <c r="CP45" t="n">
-        <v>0.4549</v>
+        <v>0.4445</v>
       </c>
       <c r="CQ45" t="n">
         <v>0</v>
@@ -19015,7 +18575,7 @@
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -19048,7 +18608,7 @@
         <v>27</v>
       </c>
       <c r="K46" t="n">
-        <v>0.0592</v>
+        <v>0.0591</v>
       </c>
       <c r="L46" t="n">
         <v>0.3333</v>
@@ -19066,13 +18626,13 @@
         <v>0.0284</v>
       </c>
       <c r="Q46" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R46" t="n">
         <v>0.1745</v>
       </c>
       <c r="S46" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="T46" t="n">
         <v>-0.1264</v>
@@ -19117,13 +18677,13 @@
         <v>-0.0945</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.0194</v>
+        <v>0.019</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.3077</v>
+        <v>0.2847</v>
       </c>
       <c r="AH46" t="n">
-        <v>11.38</v>
+        <v>11.15</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -19132,13 +18692,13 @@
         <v>-0.0075</v>
       </c>
       <c r="AK46" t="n">
-        <v>-0.085623</v>
+        <v>-0.102347</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.137737</v>
+        <v>1.169543</v>
       </c>
       <c r="AM46" t="n">
-        <v>13.77</v>
+        <v>16.95</v>
       </c>
       <c r="AN46" t="n">
         <v>0</v>
@@ -19168,10 +18728,10 @@
         <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.054261</v>
+        <v>0.053092</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.578</v>
+        <v>1.9277</v>
       </c>
       <c r="AY46" t="n">
         <v>0</v>
@@ -19323,7 +18883,7 @@
         <v>0</v>
       </c>
       <c r="CP46" t="n">
-        <v>0.5739</v>
+        <v>0.6135</v>
       </c>
       <c r="CQ46" t="n">
         <v>0</v>
@@ -19352,7 +18912,7 @@
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -19385,7 +18945,7 @@
         <v>51</v>
       </c>
       <c r="K47" t="n">
-        <v>0.1118</v>
+        <v>0.1116</v>
       </c>
       <c r="L47" t="n">
         <v>0.6274999999999999</v>
@@ -19403,13 +18963,13 @@
         <v>0.0314</v>
       </c>
       <c r="Q47" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R47" t="n">
         <v>0.0425</v>
       </c>
       <c r="S47" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="T47" t="n">
         <v>1.2836</v>
@@ -19450,28 +19010,28 @@
         <v>0.2225</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.0247</v>
+        <v>0.0264</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.4406</v>
+        <v>0.5004</v>
       </c>
       <c r="AH47" t="n">
-        <v>7.17</v>
+        <v>6.87</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.1436</v>
+        <v>0.1433</v>
       </c>
       <c r="AK47" t="n">
-        <v>-0.011832</v>
+        <v>-0.030584</v>
       </c>
       <c r="AL47" t="n">
-        <v>0.968738</v>
+        <v>1.007473</v>
       </c>
       <c r="AM47" t="n">
-        <v>-3.13</v>
+        <v>0.75</v>
       </c>
       <c r="AN47" t="n">
         <v>0</v>
@@ -19501,10 +19061,10 @@
         <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.068871</v>
+        <v>0.073798</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.1718</v>
+        <v>0.4144</v>
       </c>
       <c r="AY47" t="n">
         <v>0</v>
@@ -19519,7 +19079,7 @@
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>compressao</t>
+          <t>neutro_zona_cinza</t>
         </is>
       </c>
       <c r="BC47" t="n">
@@ -19656,7 +19216,7 @@
         <v>0</v>
       </c>
       <c r="CP47" t="n">
-        <v>0.3726</v>
+        <v>0.3849</v>
       </c>
       <c r="CQ47" t="n">
         <v>0</v>
@@ -19685,7 +19245,7 @@
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -19733,16 +19293,16 @@
         <v>2.4065</v>
       </c>
       <c r="P48" t="n">
-        <v>-0.1084</v>
+        <v>-0.0985</v>
       </c>
       <c r="Q48" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R48" t="n">
-        <v>-0.1426</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="S48" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="T48" t="n">
         <v>0.1074</v>
@@ -19790,10 +19350,10 @@
         <v>0.0288</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.1858</v>
+        <v>0.1857</v>
       </c>
       <c r="AH48" t="n">
-        <v>8.119999999999999</v>
+        <v>7.84</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -19802,13 +19362,13 @@
         <v>0.0021</v>
       </c>
       <c r="AK48" t="n">
-        <v>-0.075325</v>
+        <v>-0.089424</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.105022</v>
+        <v>1.108213</v>
       </c>
       <c r="AM48" t="n">
-        <v>10.5</v>
+        <v>10.82</v>
       </c>
       <c r="AN48" t="n">
         <v>1</v>
@@ -19838,10 +19398,10 @@
         <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>0.080497</v>
+        <v>0.080481</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.9358</v>
+        <v>1.1111</v>
       </c>
       <c r="AY48" t="n">
         <v>0</v>
@@ -19989,7 +19549,7 @@
         <v>0</v>
       </c>
       <c r="CP48" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.5312</v>
       </c>
       <c r="CQ48" t="n">
         <v>0</v>
@@ -20018,7 +19578,7 @@
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -20066,16 +19626,16 @@
         <v>-0.18</v>
       </c>
       <c r="P49" t="n">
-        <v>0.0211</v>
+        <v>0.0196</v>
       </c>
       <c r="Q49" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R49" t="n">
-        <v>0.1807</v>
+        <v>0.1758</v>
       </c>
       <c r="S49" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="T49" t="n">
         <v>-0.18</v>
@@ -20118,13 +19678,13 @@
         <v>-0.2552</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.0251</v>
+        <v>0.0242</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.5203</v>
+        <v>0.4822</v>
       </c>
       <c r="AH49" t="n">
-        <v>11.45</v>
+        <v>11.53</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -20133,13 +19693,13 @@
         <v>-0.0004</v>
       </c>
       <c r="AK49" t="n">
-        <v>-0.015437</v>
+        <v>-0.008311000000000001</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.061931</v>
+        <v>1.063986</v>
       </c>
       <c r="AM49" t="n">
-        <v>6.19</v>
+        <v>6.4</v>
       </c>
       <c r="AN49" t="n">
         <v>1</v>
@@ -20169,10 +19729,10 @@
         <v>0</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.070095</v>
+        <v>0.06743300000000001</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.2202</v>
+        <v>0.1233</v>
       </c>
       <c r="AY49" t="n">
         <v>0</v>
@@ -20320,7 +19880,7 @@
         <v>0</v>
       </c>
       <c r="CP49" t="n">
-        <v>0.4071</v>
+        <v>0.405</v>
       </c>
       <c r="CQ49" t="n">
         <v>0</v>
@@ -20349,7 +19909,7 @@
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -20382,7 +19942,7 @@
         <v>77</v>
       </c>
       <c r="K50" t="n">
-        <v>0.1689</v>
+        <v>0.1685</v>
       </c>
       <c r="L50" t="n">
         <v>0.7662</v>
@@ -20400,13 +19960,13 @@
         <v>0.0519</v>
       </c>
       <c r="Q50" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R50" t="n">
         <v>0.09950000000000001</v>
       </c>
       <c r="S50" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="T50" t="n">
         <v>0.2314</v>
@@ -20447,28 +20007,28 @@
         <v>0.2292</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.0147</v>
+        <v>0.015</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.1463</v>
+        <v>0.1579</v>
       </c>
       <c r="AH50" t="n">
-        <v>14.15</v>
+        <v>13.89</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.0391</v>
+        <v>0.039</v>
       </c>
       <c r="AK50" t="n">
-        <v>0.023197</v>
+        <v>0.002942</v>
       </c>
       <c r="AL50" t="n">
-        <v>1.108987</v>
+        <v>1.089624</v>
       </c>
       <c r="AM50" t="n">
-        <v>10.9</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="AN50" t="n">
         <v>1</v>
@@ -20498,10 +20058,10 @@
         <v>0</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.040931</v>
+        <v>0.041868</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.5667</v>
+        <v>0.0703</v>
       </c>
       <c r="AY50" t="n">
         <v>0</v>
@@ -20653,7 +20213,7 @@
         <v>0</v>
       </c>
       <c r="CP50" t="n">
-        <v>0.4736</v>
+        <v>0.4216</v>
       </c>
       <c r="CQ50" t="n">
         <v>0</v>
@@ -39201,12 +38761,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -39237,7 +38797,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -39417,12 +38977,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -39633,7 +39193,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -39669,7 +39229,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -39705,7 +39265,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -39741,7 +39301,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -39813,7 +39373,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -39849,12 +39409,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
+          <t>alerta_executor_nivel_B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -40029,7 +39589,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -41003,7 +40563,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.5202</v>
+        <v>0.5854</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -41069,7 +40629,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.6329</v>
+        <v>0.5837</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -41135,7 +40695,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.4753</v>
+        <v>0.457</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -41201,7 +40761,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.4402</v>
+        <v>0.4484</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -41304,20 +40864,20 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.5767</v>
+        <v>0.4864</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -41544,10 +41104,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -41559,20 +41119,20 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0.4649</v>
+        <v>0.4335</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>compressao</t>
         </is>
       </c>
     </row>
@@ -41629,7 +41189,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0.4426</v>
+        <v>0.4588</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -41787,7 +41347,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0.5139</v>
+        <v>0.5464</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -41929,7 +41489,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -41945,7 +41505,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0.4417</v>
+        <v>0.4081</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -41954,7 +41514,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>compressao</t>
         </is>
       </c>
     </row>
@@ -42011,7 +41571,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.5735</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -42058,7 +41618,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -42068,25 +41628,25 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0.5599</v>
+        <v>0.4507</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>expansao</t>
+          <t>neutro_zona_cinza</t>
         </is>
       </c>
     </row>
@@ -42143,7 +41703,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0.4797</v>
+        <v>0.4851</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -42193,7 +41753,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
@@ -42209,7 +41769,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0.2851</v>
+        <v>0.3065</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -42218,7 +41778,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>compressao</t>
+          <t>neutro_zona_cinza</t>
         </is>
       </c>
     </row>
@@ -42317,7 +41877,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0.5003</v>
+        <v>0.5122</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -42429,7 +41989,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0.4622</v>
+        <v>0.4701</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -42438,7 +41998,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>expansao</t>
         </is>
       </c>
     </row>
@@ -42541,7 +42101,7 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0.4961</v>
+        <v>0.5047</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -42603,15 +42163,15 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0.6001</v>
+        <v>0.456</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -42746,7 +42306,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -42761,15 +42321,15 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0.3936</v>
+        <v>0.4524</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -42861,7 +42421,7 @@
         <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
@@ -42873,20 +42433,20 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0.4687</v>
+        <v>0.4936</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>compressao</t>
         </is>
       </c>
     </row>
@@ -42924,7 +42484,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>1</v>
@@ -42939,15 +42499,15 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0.5308</v>
+        <v>0.5029</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -43009,7 +42569,7 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0.4186</v>
+        <v>0.3904</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -43018,7 +42578,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>expansao</t>
         </is>
       </c>
     </row>
@@ -43059,7 +42619,7 @@
         <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
@@ -43071,20 +42631,20 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0.5014</v>
+        <v>0.5104</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>compressao</t>
         </is>
       </c>
     </row>
@@ -43132,16 +42692,16 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
+          <t>alerta_executor_nivel_B</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0.5934</v>
+        <v>0.5923</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -43391,7 +42951,7 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0.4037</v>
+        <v>0.3908</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -43457,7 +43017,7 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0.3961</v>
+        <v>0.4112</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -43523,7 +43083,7 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0.474</v>
+        <v>0.4437</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -43589,7 +43149,7 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0.479</v>
+        <v>0.481</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -43774,7 +43334,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>1</v>
@@ -43789,15 +43349,15 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0.5082</v>
+        <v>0.4713</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -43859,7 +43419,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0.5165</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -43925,7 +43485,7 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0.3389</v>
+        <v>0.3546</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -43991,7 +43551,7 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0.5809</v>
+        <v>0.5564</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -44057,7 +43617,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0.4228</v>
+        <v>0.4282</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -44353,7 +43913,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0.5382</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -44741,7 +44301,7 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0.4074</v>
+        <v>0.415</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -44853,7 +44413,7 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0.3755</v>
+        <v>0.3921</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -44919,7 +44479,7 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0.4613</v>
+        <v>0.4123</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -45027,7 +44587,7 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0.4952</v>
+        <v>0.4818</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -45093,7 +44653,7 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0.3701</v>
+        <v>0.3844</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -45201,7 +44761,7 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0.3086</v>
+        <v>0.3134</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -45313,7 +44873,7 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0.5204</v>
+        <v>0.4546</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -45379,7 +44939,7 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0.4394</v>
+        <v>0.3999</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -45709,7 +45269,7 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0.6287</v>
+        <v>0.6371</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -45909,7 +45469,7 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0.5434</v>
+        <v>0.5161</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -45975,7 +45535,7 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>0.4549</v>
+        <v>0.4445</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -46041,7 +45601,7 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0.5739</v>
+        <v>0.6135</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -46137,7 +45697,7 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
         <v>1</v>
@@ -46153,7 +45713,7 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0.3726</v>
+        <v>0.3849</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -46162,7 +45722,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>compressao</t>
+          <t>neutro_zona_cinza</t>
         </is>
       </c>
     </row>
@@ -46219,7 +45779,7 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.5312</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -46331,7 +45891,7 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0.4071</v>
+        <v>0.405</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -46443,7 +46003,7 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0.4736</v>
+        <v>0.4216</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -46669,7 +46229,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -46679,7 +46239,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -46699,7 +46259,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -46729,7 +46289,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -46769,7 +46329,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30">
@@ -46789,7 +46349,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="32">

--- a/saidas/ordens_dia/ordem_dia_2026_07_29_executor_v5_5.xlsx
+++ b/saidas/ordens_dia/ordem_dia_2026_07_29_executor_v5_5.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DE4"/>
+  <dimension ref="A1:DE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -985,22 +985,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GOAU4</t>
+          <t>BHIA3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Call delta~45 naked (quase ATM, ~0.9σ, 20d)</t>
+          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1020,40 +1020,40 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>114</v>
+        <v>48</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2495</v>
+        <v>0.105</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.8333</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3793</v>
+        <v>0.4516</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7677</v>
+        <v>1.2856</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3161</v>
+        <v>0.7368</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0615</v>
+        <v>-0.0485</v>
       </c>
       <c r="R2" t="n">
         <v>437</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3719</v>
+        <v>0.0118</v>
       </c>
       <c r="T2" t="n">
-        <v>267</v>
+        <v>379</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1909</v>
+        <v>0.6655</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0518</v>
+        <v>0.1171</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -1067,49 +1067,49 @@
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>0.259</v>
+        <v>0.8411</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.8094</v>
+        <v>2.6285</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.1899</v>
+        <v>0.6645</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.259</v>
+        <v>0.8411</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0668</v>
+        <v>0.166</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.2136</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1303</v>
+        <v>0.331</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.0158</v>
+        <v>0.0381</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.3362</v>
+        <v>0.1929</v>
       </c>
       <c r="AI2" t="n">
-        <v>10.77</v>
+        <v>0.76</v>
       </c>
       <c r="AJ2" t="n">
-        <v>11.17</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.0476</v>
+        <v>0.0699</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.118415</v>
+        <v>-0.2154</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.128108</v>
+        <v>1.201075</v>
       </c>
       <c r="AN2" t="n">
-        <v>12.81</v>
+        <v>20.11</v>
       </c>
       <c r="AO2" t="n">
         <v>1</v>
@@ -1118,31 +1118,31 @@
         <v>1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.119918</v>
+        <v>1.034456</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.191264</v>
+        <v>1.08</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.874264</v>
+        <v>0.816703</v>
       </c>
       <c r="AV2" t="n">
         <v>1</v>
       </c>
       <c r="AW2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.044087</v>
+        <v>0.106458</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.686</v>
+        <v>2.0233</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>expansao</t>
         </is>
       </c>
       <c r="BD2" t="n">
@@ -1166,21 +1166,17 @@
       <c r="BE2" t="n">
         <v>0</v>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="BI2" t="n">
         <v>1</v>
       </c>
@@ -1188,28 +1184,28 @@
         <v>1</v>
       </c>
       <c r="BK2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
         <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="BP2" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.6464646464646464</v>
+        <v>0.7171717171717171</v>
       </c>
       <c r="BR2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
         <v>1</v>
@@ -1219,59 +1215,59 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>exec_bilateral</t>
+          <t>exec_baixa</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>expansion_moderada</t>
+          <t>sem_edge</t>
         </is>
       </c>
       <c r="BW2" t="n">
-        <v>0.6917</v>
+        <v>0.5042</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.7129</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.5051</v>
+        <v>0.4399</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.3600266258768599</v>
+        <v>0.4832765979561717</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.5231262931542173</v>
+        <v>0.6473258788685476</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.6308080237461189</v>
+        <v>0.6231809318200072</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.6308080237461189</v>
+        <v>0.6473258788685476</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.4137931034482759</v>
+        <v>0.7094017094017094</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.3302752293577982</v>
+        <v>0.5971223021582733</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.6187050359712231</v>
+        <v>0.6505376344086021</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.5548387096774193</v>
+        <v>0.7960526315789473</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.7592592592592593</v>
+        <v>0.8382352941176471</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.3106060606060606</v>
+        <v>0.4042553191489361</v>
       </c>
       <c r="CJ2" t="n">
         <v>0</v>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>expansao_moderada_sem_exec_forte</t>
+          <t>instabilidade_regressao</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
@@ -1281,7 +1277,7 @@
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>RV_RANK</t>
         </is>
       </c>
       <c r="CN2" t="n">
@@ -1291,13 +1287,13 @@
         <v>0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.5923</v>
+        <v>0.6384</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.5923</v>
+        <v>0.6384</v>
       </c>
       <c r="CS2" t="n">
         <v>0</v>
@@ -1305,17 +1301,17 @@
       <c r="CT2" t="inlineStr"/>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>Call delta~50 naked (ATM, máximo gamma)</t>
+          <t>Put delta~-50 naked (ATM, máximo gamma)</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>Call delta~40 naked (ligeiramente mais OTM)</t>
+          <t>Put delta~-40 naked (ligeiramente mais OTM)</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>OTM extremo (&lt;delta~20) sem vol prevista muito forte</t>
+          <t>OTM extremo sem vol prevista muito forte</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
@@ -1325,17 +1321,17 @@
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>naked_30: esp=+0.190 | spread_35_20: esp=+0.067 | spread_45_25: esp=+0.078 | spread_45_15: esp=+0.130</t>
+          <t>naked_30: esp=+0.664 | spread_35_20: esp=+0.166 | spread_45_25: esp=+0.214 | spread_45_15: esp=+0.331</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>[Empírico] Call delta~45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.259 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.841 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>media</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr">
@@ -1345,17 +1341,17 @@
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>100% do prêmio pago</t>
+          <t>80% do prêmio pago</t>
         </is>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>50% do prêmio pago</t>
+          <t>40% do prêmio pago</t>
         </is>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>Edge forte — aguardar dobrar o prêmio. Stop 50%.</t>
+          <t>Regra 80/40: realizar 80%, stop 40%.</t>
         </is>
       </c>
     </row>
@@ -1370,131 +1366,135 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BHIA3</t>
+          <t>KLBN11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Compra CALL (VETADA)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
+          <t>VETADA — esperança histórica insuficiente</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>aprovado_executor_nivel_A</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L3" t="n">
-        <v>0.105</v>
+        <v>0.0941</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8333</v>
+        <v>0.6512</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4516</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2835</v>
+        <v>0.2666</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7368</v>
+        <v>-0.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.0485</v>
+        <v>-0.0437</v>
       </c>
       <c r="R3" t="n">
         <v>437</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0118</v>
+        <v>-0.0717</v>
       </c>
       <c r="T3" t="n">
-        <v>379</v>
+        <v>300</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6643</v>
+        <v>-0.1354</v>
       </c>
       <c r="V3" t="n">
-        <v>0.117</v>
+        <v>0.0177</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>naked_45</t>
+          <t>nenhuma</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
+          <t>spread_35_20,spread_45_15,spread_45_25</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>esperanca</t>
+        </is>
+      </c>
       <c r="Z3" t="n">
-        <v>0.8399</v>
+        <v>-0.18</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.6248</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6633</v>
+        <v>-0.1364</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8399</v>
+        <v>-0.1831</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.166</v>
+        <v>-0.0723</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.2136</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.331</v>
+        <v>-0.1207</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0378</v>
+        <v>0.0106</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.1881</v>
+        <v>0.1926</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.77</v>
+        <v>18.02</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.7</v>
+        <v>18.46</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.0698</v>
+        <v>-0.0127</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.208582</v>
+        <v>0.041081</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.181753</v>
+        <v>1.172216</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.18</v>
+        <v>17.22</v>
       </c>
       <c r="AO3" t="n">
         <v>1</v>
@@ -1509,25 +1509,25 @@
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.034456</v>
+        <v>1.114435</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.08</v>
+        <v>1.115445</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.816703</v>
+        <v>0.876011</v>
       </c>
       <c r="AV3" t="n">
         <v>1</v>
       </c>
       <c r="AW3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.105469</v>
+        <v>0.029586</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.9777</v>
+        <v>1.3885</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1546,20 +1546,20 @@
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="BI3" t="n">
@@ -1575,84 +1575,84 @@
         <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN3" t="n">
         <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="BP3" t="n">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.7171717171717171</v>
+        <v>0.3434343434343434</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>exec_baixa</t>
+          <t>exec_alta</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>sem_edge</t>
+          <t>exec_expansion_har</t>
         </is>
       </c>
       <c r="BW3" t="n">
-        <v>0.5042</v>
+        <v>0.6368</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.7129</v>
+        <v>0.6546</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.4399</v>
+        <v>0.4917</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.4832765979561717</v>
+        <v>0.3478669257672033</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.6473258788685476</v>
+        <v>0.5742751832410374</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.6231809318200072</v>
+        <v>0.1717746127157639</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.6473258788685476</v>
+        <v>0.5742751832410374</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.7094017094017094</v>
+        <v>0.5181818181818182</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.5971223021582733</v>
+        <v>0.4956521739130435</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.6505376344086021</v>
+        <v>0.5811965811965812</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.7960526315789473</v>
+        <v>0.4503311258278146</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.8382352941176471</v>
+        <v>0</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.4042553191489361</v>
+        <v>0</v>
       </c>
       <c r="CJ3" t="n">
         <v>0</v>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>instabilidade_regressao</t>
+          <t>har_fallback_aprovado_expansao</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
@@ -1662,436 +1662,51 @@
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>RV_RANK</t>
+          <t>HAR</t>
         </is>
       </c>
       <c r="CN3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>0.6027397260273972</v>
       </c>
       <c r="CP3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.6371</v>
+        <v>0.5522</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.6371</v>
+        <v>0.5522</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT3" t="inlineStr"/>
-      <c r="CU3" t="inlineStr">
-        <is>
-          <t>Put delta~-50 naked (ATM, máximo gamma)</t>
-        </is>
-      </c>
-      <c r="CV3" t="inlineStr">
-        <is>
-          <t>Put delta~-40 naked (ligeiramente mais OTM)</t>
-        </is>
-      </c>
-      <c r="CW3" t="inlineStr">
-        <is>
-          <t>OTM extremo sem vol prevista muito forte</t>
-        </is>
-      </c>
-      <c r="CX3" t="inlineStr">
-        <is>
-          <t>~0.45</t>
-        </is>
-      </c>
-      <c r="CY3" t="inlineStr">
-        <is>
-          <t>naked_30: esp=+0.663 | spread_35_20: esp=+0.166 | spread_45_25: esp=+0.214 | spread_45_15: esp=+0.331</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>vetado_esperanca_historica</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr"/>
+      <c r="CV3" t="inlineStr"/>
+      <c r="CW3" t="inlineStr"/>
+      <c r="CX3" t="inlineStr"/>
+      <c r="CY3" t="inlineStr"/>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.840 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="DB3" t="inlineStr">
-        <is>
-          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.053%/dia | carry 20 pregões: 1.06%]</t>
-        </is>
-      </c>
-      <c r="DC3" t="inlineStr">
-        <is>
-          <t>80% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="DD3" t="inlineStr">
-        <is>
-          <t>40% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="DE3" t="inlineStr">
-        <is>
-          <t>Regra 80/40: realizar 80%, stop 40%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>v5.5_executor_diario</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>46232</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>KLBN11</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Compra CALL (VETADA)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>VETADA — esperança histórica insuficiente</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>aprovado_executor_nivel_A</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>43</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.0941</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.6512</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.2667</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-0.0437</v>
-      </c>
-      <c r="R4" t="n">
-        <v>437</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-0.0717</v>
-      </c>
-      <c r="T4" t="n">
-        <v>300</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-0.1354</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.0177</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>nenhuma</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>spread_35_20,spread_45_15,spread_45_25</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>esperanca</t>
-        </is>
-      </c>
-      <c r="Z4" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-0.1364</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-0.1831</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-0.0723</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-0.08649999999999999</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-0.1207</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.0106</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.1902</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>18.04</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>18.48</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>-0.0127</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0.042047</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.17222</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>17.22</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1.114435</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.115445</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0.876011</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0.029493</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.4256</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>forte</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>expansao</t>
-        </is>
-      </c>
-      <c r="BD4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="BI4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>39</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>66</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>0.3434343434343434</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>exec_alta</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>exec_expansion_har</t>
-        </is>
-      </c>
-      <c r="BW4" t="n">
-        <v>0.6368</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>0.6546</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>0.4917</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0.3478669257672033</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>0.5742751832410374</v>
-      </c>
-      <c r="CB4" t="n">
-        <v>0.1717746127157639</v>
-      </c>
-      <c r="CC4" t="n">
-        <v>0.5742751832410374</v>
-      </c>
-      <c r="CD4" t="n">
-        <v>0.5181818181818182</v>
-      </c>
-      <c r="CE4" t="n">
-        <v>0.4956521739130435</v>
-      </c>
-      <c r="CF4" t="n">
-        <v>0.5811965811965812</v>
-      </c>
-      <c r="CG4" t="n">
-        <v>0.4503311258278146</v>
-      </c>
-      <c r="CH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK4" t="inlineStr">
-        <is>
-          <t>har_fallback_aprovado_expansao</t>
-        </is>
-      </c>
-      <c r="CL4" t="inlineStr">
-        <is>
-          <t>threshold_por_ativo</t>
-        </is>
-      </c>
-      <c r="CM4" t="inlineStr">
-        <is>
-          <t>HAR</t>
-        </is>
-      </c>
-      <c r="CN4" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO4" t="n">
-        <v>0.6027397260273972</v>
-      </c>
-      <c r="CP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ4" t="n">
-        <v>0.5564</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>0.5564</v>
-      </c>
-      <c r="CS4" t="n">
-        <v>1</v>
-      </c>
-      <c r="CT4" t="inlineStr">
-        <is>
-          <t>vetado_esperanca_historica</t>
-        </is>
-      </c>
-      <c r="CU4" t="inlineStr"/>
-      <c r="CV4" t="inlineStr"/>
-      <c r="CW4" t="inlineStr"/>
-      <c r="CX4" t="inlineStr"/>
-      <c r="CY4" t="inlineStr"/>
-      <c r="CZ4" t="inlineStr">
-        <is>
-          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
-        </is>
-      </c>
-      <c r="DA4" t="inlineStr">
-        <is>
           <t>vetada</t>
         </is>
       </c>
-      <c r="DB4" t="inlineStr"/>
-      <c r="DC4" t="inlineStr"/>
-      <c r="DD4" t="inlineStr"/>
-      <c r="DE4" t="inlineStr"/>
+      <c r="DB3" t="inlineStr"/>
+      <c r="DC3" t="inlineStr"/>
+      <c r="DD3" t="inlineStr"/>
+      <c r="DE3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2197,70 +1812,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ITSA4</t>
+          <t>EZTC3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SINAL FRACO (reverter)</t>
+          <t>NO LUCRO (segurar)</t>
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46221</v>
+        <v>46227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Compra CALL</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>spread_45_15</t>
+          <t>naked_45</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H2" t="n">
-        <v>13.61</v>
+        <v>11.4</v>
       </c>
       <c r="I2" t="n">
-        <v>13.52</v>
+        <v>11.08</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.66</v>
+        <v>-2.81</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.257</v>
+        <v>0.531</v>
       </c>
       <c r="L2" t="n">
-        <v>0.425</v>
+        <v>0.49</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.255</v>
+        <v>0.041</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.094</v>
+        <v>1.964</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0039</v>
+        <v>-0.1068</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>razao=0.09 &lt; 0.6 | M=-0.26 — ativo foi contra, tese falhou</t>
+          <t>M=0.53 ≥ BE=0.49 mas &lt; alvo | lucro≈+0.04DP — trailing</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JHSF3</t>
+          <t>BBDC4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2269,11 +1884,11 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46211</v>
+        <v>46231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2282,22 +1897,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="H3" t="n">
-        <v>10.35</v>
+        <v>18.77</v>
       </c>
       <c r="I3" t="n">
-        <v>10.6</v>
+        <v>18.35</v>
       </c>
       <c r="J3" t="n">
-        <v>2.42</v>
+        <v>-2.24</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.022</v>
+        <v>-0.499</v>
       </c>
       <c r="L3" t="n">
         <v>0.49</v>
@@ -2309,21 +1924,21 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.241</v>
+        <v>0.55</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0159</v>
+        <v>0.0228</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>razao=0.24 &lt; 0.6 | M=-0.02 — ativo foi contra, tese falhou</t>
+          <t>razao=0.55 &lt; 0.6 | M=-0.50 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VALE3</t>
+          <t>ITSA4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2332,11 +1947,11 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46212</v>
+        <v>46221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Compra CALL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2345,22 +1960,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H4" t="n">
-        <v>73.15000000000001</v>
+        <v>13.61</v>
       </c>
       <c r="I4" t="n">
-        <v>75.34999999999999</v>
+        <v>13.49</v>
       </c>
       <c r="J4" t="n">
-        <v>3.01</v>
+        <v>-0.88</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.209</v>
+        <v>-0.286</v>
       </c>
       <c r="L4" t="n">
         <v>0.425</v>
@@ -2372,21 +1987,21 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.485</v>
+        <v>0.066</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0212</v>
+        <v>0.0028</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>razao=0.48 &lt; 0.6 | M=-0.21 — ativo foi contra, tese falhou</t>
+          <t>razao=0.07 &lt; 0.6 | M=-0.29 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>YDUQ3</t>
+          <t>JHSF3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2395,7 +2010,7 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46230</v>
+        <v>46211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2408,22 +2023,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>7.94</v>
+        <v>10.35</v>
       </c>
       <c r="I5" t="n">
-        <v>8.16</v>
+        <v>10.58</v>
       </c>
       <c r="J5" t="n">
-        <v>2.77</v>
+        <v>2.22</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.02</v>
+        <v>-0.001</v>
       </c>
       <c r="L5" t="n">
         <v>0.49</v>
@@ -2435,30 +2050,30 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.357</v>
+        <v>0.249</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.0271</v>
+        <v>-0.0167</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>razao=0.36 &lt; 0.6 | M=-0.02 — ativo foi contra, tese falhou</t>
+          <t>razao=0.25 &lt; 0.6 | M=-0.00 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SBFG3</t>
+          <t>VALE3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SINAL FRACO (segurar)</t>
+          <t>SINAL FRACO (reverter)</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46228</v>
+        <v>46212</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2467,65 +2082,65 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>naked_45</t>
+          <t>spread_45_15</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>9.359999999999999</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>9.32</v>
+        <v>75.05</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.43</v>
+        <v>2.6</v>
       </c>
       <c r="K6" t="n">
-        <v>0.247</v>
+        <v>-0.147</v>
       </c>
       <c r="L6" t="n">
-        <v>0.49</v>
+        <v>0.425</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.243</v>
+        <v>-0.255</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.213</v>
+        <v>0.44</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0139</v>
+        <v>0.0194</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>razao=0.21 &lt; 0.6 | M=0.25 — movimento OK, modelo ruidoso</t>
+          <t>razao=0.44 &lt; 0.6 | M=-0.15 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>SBFG3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MANTER</t>
+          <t>SINAL FRACO (segurar)</t>
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46231</v>
+        <v>46228</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2534,57 +2149,57 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H7" t="n">
-        <v>18.77</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>18.42</v>
+        <v>9.32</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.86</v>
+        <v>-0.43</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.458</v>
+        <v>0.247</v>
       </c>
       <c r="L7" t="n">
         <v>0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.32</v>
+        <v>-0.243</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.649</v>
+        <v>0.235</v>
       </c>
       <c r="P7" t="n">
-        <v>0.026</v>
+        <v>-0.0153</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>M=-0.46 | razao=0.65 | 1/20d</t>
+          <t>razao=0.23 &lt; 0.6 | M=0.25 — movimento OK, modelo ruidoso</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BHIA3</t>
+          <t>YDUQ3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MANTER</t>
+          <t>SINAL FRACO (segurar)</t>
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2597,48 +2212,48 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H8" t="n">
-        <v>0.79</v>
+        <v>7.94</v>
       </c>
       <c r="I8" t="n">
-        <v>0.77</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.53</v>
+        <v>2.52</v>
       </c>
       <c r="K8" t="n">
-        <v>0.382</v>
+        <v>0.001</v>
       </c>
       <c r="L8" t="n">
         <v>0.49</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.108</v>
+        <v>-0.32</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.978</v>
+        <v>0.368</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2086</v>
+        <v>-0.0279</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>M=0.38 | razao=1.98 | 1/20d</t>
+          <t>razao=0.37 &lt; 0.6 | M=0.00 — movimento OK, modelo ruidoso</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CYRE3</t>
+          <t>BHIA3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2647,7 +2262,7 @@
         </is>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2660,48 +2275,48 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H9" t="n">
-        <v>20.7</v>
+        <v>0.79</v>
       </c>
       <c r="I9" t="n">
-        <v>20.68</v>
+        <v>0.76</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1</v>
+        <v>-3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>0.215</v>
+        <v>0.456</v>
       </c>
       <c r="L9" t="n">
         <v>0.49</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.275</v>
+        <v>-0.034</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.928</v>
+        <v>2.023</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.0603</v>
+        <v>-0.2154</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>M=0.22 | razao=0.93 | 3/20d</t>
+          <t>M=0.46 | razao=2.02 | 1/20d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EZTC3</t>
+          <t>CYRE3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2729,35 +2344,35 @@
         <v>17</v>
       </c>
       <c r="H10" t="n">
-        <v>11.4</v>
+        <v>20.7</v>
       </c>
       <c r="I10" t="n">
-        <v>11.15</v>
+        <v>20.77</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.19</v>
+        <v>0.34</v>
       </c>
       <c r="K10" t="n">
-        <v>0.468</v>
+        <v>0.173</v>
       </c>
       <c r="L10" t="n">
         <v>0.49</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.022</v>
+        <v>-0.317</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.928</v>
+        <v>0.846</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1023</v>
+        <v>-0.054</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>M=0.47 | razao=1.93 | 3/20d</t>
+          <t>M=0.17 | razao=0.85 | 3/20d</t>
         </is>
       </c>
     </row>
@@ -2795,32 +2410,32 @@
         <v>44.64</v>
       </c>
       <c r="I11" t="n">
-        <v>47.54</v>
+        <v>47.51</v>
       </c>
       <c r="J11" t="n">
-        <v>6.5</v>
+        <v>6.43</v>
       </c>
       <c r="K11" t="n">
-        <v>0.614</v>
+        <v>0.606</v>
       </c>
       <c r="L11" t="n">
         <v>0.751</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.137</v>
+        <v>-0.145</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.29</v>
+        <v>1.313</v>
       </c>
       <c r="P11" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>M=0.61 | razao=1.29 | 9/20d</t>
+          <t>M=0.61 | razao=1.31 | 9/20d</t>
         </is>
       </c>
     </row>
@@ -2858,13 +2473,13 @@
         <v>5.27</v>
       </c>
       <c r="I12" t="n">
-        <v>5.33</v>
+        <v>5.31</v>
       </c>
       <c r="J12" t="n">
-        <v>1.14</v>
+        <v>0.76</v>
       </c>
       <c r="K12" t="n">
-        <v>0.074</v>
+        <v>0.12</v>
       </c>
       <c r="L12" t="n">
         <v>0.49</v>
@@ -2876,14 +2491,14 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.709</v>
+        <v>0.732</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.0365</v>
+        <v>-0.038</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>M=0.07 | razao=0.71 | 2/20d</t>
+          <t>M=0.12 | razao=0.73 | 2/20d</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3011,19 +2626,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GOAU4</t>
+          <t>BHIA3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3362</v>
+        <v>0.1929</v>
       </c>
       <c r="D2" t="n">
-        <v>1.128108</v>
+        <v>1.201075</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3031,16 +2646,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.1909</v>
+        <v>0.6655</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>media</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Call delta~45 naked (quase ATM, ~0.9σ, 20d)</t>
+          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -3050,32 +2665,32 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>100% do prêmio pago</t>
+          <t>80% do prêmio pago</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>50% do prêmio pago</t>
+          <t>40% do prêmio pago</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Edge forte — aguardar dobrar o prêmio. Stop 50%.</t>
+          <t>Regra 80/40: realizar 80%, stop 40%.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Call delta~50 naked (ATM, máximo gamma)</t>
+          <t>Put delta~-50 naked (ATM, máximo gamma)</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Call delta~40 naked (ligeiramente mais OTM)</t>
+          <t>Put delta~-40 naked (ligeiramente mais OTM)</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>OTM extremo (&lt;delta~20) sem vol prevista muito forte</t>
+          <t>OTM extremo sem vol prevista muito forte</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -3085,17 +2700,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[Empírico] Call delta~45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.259 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.841 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>0.0158</v>
+        <v>0.0381</v>
       </c>
       <c r="S2" t="n">
-        <v>25.1</v>
+        <v>60.5</v>
       </c>
       <c r="T2" t="n">
-        <v>28.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -3106,19 +2721,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BHIA3</t>
+          <t>KLBN11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Compra CALL (VETADA)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1881</v>
+        <v>0.1926</v>
       </c>
       <c r="D3" t="n">
-        <v>1.181753</v>
+        <v>1.172216</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3126,136 +2741,41 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.6643</v>
+        <v>-0.1354</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>vetada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.053%/dia | carry 20 pregões: 1.06%]</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>80% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>40% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Regra 80/40: realizar 80%, stop 40%.</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Put delta~-50 naked (ATM, máximo gamma)</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Put delta~-40 naked (ligeiramente mais OTM)</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>OTM extremo sem vol prevista muito forte</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>~0.45</t>
-        </is>
-      </c>
+          <t>VETADA — esperança histórica insuficiente</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.840 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0.0378</v>
+        <v>0.0106</v>
       </c>
       <c r="S3" t="n">
-        <v>60</v>
+        <v>16.8</v>
       </c>
       <c r="T3" t="n">
-        <v>70.90000000000001</v>
+        <v>19.7</v>
       </c>
       <c r="U3" t="inlineStr">
-        <is>
-          <t>Se IV_mercado &lt; vol_anualizada_pct → opção barata (compra favorável)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>KLBN11</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Compra CALL (VETADA)</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.1902</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.17222</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>forte</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>-0.1354</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>vetada</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>VETADA — esperança histórica insuficiente</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
-        <v>0.0106</v>
-      </c>
-      <c r="S4" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="T4" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="U4" t="inlineStr">
         <is>
           <t>Se IV_mercado &lt; vol_anualizada_pct → opção barata (compra favorável)</t>
         </is>
@@ -3936,13 +3456,13 @@
         <v>-0.0113</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.077108</v>
+        <v>0.07877000000000001</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.915731</v>
+        <v>0.912408</v>
       </c>
       <c r="AM2" t="n">
-        <v>-8.43</v>
+        <v>-8.76</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -3975,7 +3495,7 @@
         <v>0.04714</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.6357</v>
+        <v>1.671</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -4127,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.5854</v>
+        <v>0.589</v>
       </c>
       <c r="CQ2" t="n">
         <v>0</v>
@@ -4254,13 +3774,13 @@
         <v>0.219</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0199</v>
+        <v>0.0205</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0646</v>
+        <v>0.079</v>
       </c>
       <c r="AH3" t="n">
-        <v>42.57</v>
+        <v>41.76</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -4269,13 +3789,13 @@
         <v>0.0304</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.07413699999999999</v>
+        <v>0.054528</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.256801</v>
+        <v>1.226307</v>
       </c>
       <c r="AM3" t="n">
-        <v>25.68</v>
+        <v>22.63</v>
       </c>
       <c r="AN3" t="n">
         <v>1</v>
@@ -4305,10 +3825,10 @@
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.055484</v>
+        <v>0.057108</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.3362</v>
+        <v>0.9548</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
@@ -4456,7 +3976,7 @@
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.5837</v>
+        <v>0.5426</v>
       </c>
       <c r="CQ3" t="n">
         <v>0</v>
@@ -4539,7 +4059,7 @@
         <v>437</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3141</v>
+        <v>0.3142</v>
       </c>
       <c r="S4" t="n">
         <v>223</v>
@@ -4583,13 +4103,13 @@
         <v>0.3812</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0135</v>
+        <v>0.0142</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.4116</v>
+        <v>0.4666</v>
       </c>
       <c r="AH4" t="n">
-        <v>42.05</v>
+        <v>41.82</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -4598,13 +4118,13 @@
         <v>0.0011</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.007856999999999999</v>
+        <v>-0.011136</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.044836</v>
+        <v>1.039701</v>
       </c>
       <c r="AM4" t="n">
-        <v>4.48</v>
+        <v>3.97</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
@@ -4634,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.037658</v>
+        <v>0.039706</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.2086</v>
+        <v>0.2805</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
@@ -4789,7 +4309,7 @@
         <v>1</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.457</v>
+        <v>0.4532</v>
       </c>
       <c r="CQ4" t="n">
         <v>0</v>
@@ -4916,13 +4436,13 @@
         <v>0.2479</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0156</v>
+        <v>0.0158</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.5063</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="AH5" t="n">
-        <v>75.34999999999999</v>
+        <v>75.05</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -4931,13 +4451,13 @@
         <v>0.2318</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.021164</v>
+        <v>0.019406</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.977406</v>
+        <v>0.980819</v>
       </c>
       <c r="AM5" t="n">
-        <v>-2.26</v>
+        <v>-1.92</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
@@ -4967,10 +4487,10 @@
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.043663</v>
+        <v>0.044068</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.4847</v>
+        <v>0.4404</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
@@ -4985,7 +4505,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>compressao</t>
+          <t>neutro_zona_cinza</t>
         </is>
       </c>
       <c r="BC5" t="n">
@@ -5122,7 +4642,7 @@
         <v>1</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.4484</v>
+        <v>0.4425</v>
       </c>
       <c r="CQ5" t="n">
         <v>0</v>
@@ -5177,7 +4697,7 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -5228,34 +4748,34 @@
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
-        <v>0.3261</v>
+        <v>0.3257</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.0191</v>
+        <v>1.0178</v>
       </c>
       <c r="AA6" t="n">
         <v>0.2411</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.3261</v>
+        <v>0.3257</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0696</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.0919</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.1452</v>
+        <v>0.1448</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0143</v>
+        <v>0.0148</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.3628</v>
+        <v>0.399</v>
       </c>
       <c r="AH6" t="n">
-        <v>18.42</v>
+        <v>18.35</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -5264,13 +4784,13 @@
         <v>0.09909999999999999</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.025985</v>
+        <v>0.022766</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.072745</v>
+        <v>1.06145</v>
       </c>
       <c r="AM6" t="n">
-        <v>7.27</v>
+        <v>6.15</v>
       </c>
       <c r="AN6" t="n">
         <v>1</v>
@@ -5300,10 +4820,10 @@
         <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.040034</v>
+        <v>0.041393</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.6491</v>
+        <v>0.55</v>
       </c>
       <c r="AY6" t="n">
         <v>0</v>
@@ -5313,7 +4833,7 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -5455,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.4864</v>
+        <v>0.4692</v>
       </c>
       <c r="CQ6" t="n">
         <v>0</v>
@@ -5586,13 +5106,13 @@
         <v>-0.0296</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0229</v>
+        <v>0.0245</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.4335</v>
+        <v>0.4982</v>
       </c>
       <c r="AH7" t="n">
-        <v>15.5</v>
+        <v>15.32</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -5601,13 +5121,13 @@
         <v>0.0017</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.036817</v>
+        <v>0.032683</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.968639</v>
+        <v>0.940384</v>
       </c>
       <c r="AM7" t="n">
-        <v>-3.14</v>
+        <v>-5.96</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
@@ -5637,10 +5157,10 @@
         <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.063774</v>
+        <v>0.068329</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.5773</v>
+        <v>0.4783</v>
       </c>
       <c r="AY7" t="n">
         <v>0</v>
@@ -5792,7 +5312,7 @@
         <v>0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.4335</v>
+        <v>0.4107</v>
       </c>
       <c r="CQ7" t="n">
         <v>0</v>
@@ -5922,10 +5442,10 @@
         <v>0.0306</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.2238</v>
+        <v>0.2271</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.77</v>
+        <v>4.76</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -5934,13 +5454,13 @@
         <v>0.0469</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.005413</v>
+        <v>0.005318</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.117832</v>
+        <v>1.114496</v>
       </c>
       <c r="AM8" t="n">
-        <v>11.78</v>
+        <v>11.45</v>
       </c>
       <c r="AN8" t="n">
         <v>1</v>
@@ -5970,10 +5490,10 @@
         <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.085285</v>
+        <v>0.08550099999999999</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0635</v>
+        <v>0.0622</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
@@ -6125,7 +5645,7 @@
         <v>1</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.4588</v>
+        <v>0.458</v>
       </c>
       <c r="CQ8" t="n">
         <v>0</v>
@@ -6255,10 +5775,10 @@
         <v>0.0198</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.4888</v>
+        <v>0.486</v>
       </c>
       <c r="AH9" t="n">
-        <v>47.54</v>
+        <v>47.51</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -6267,13 +5787,13 @@
         <v>0.0275</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.07137</v>
+        <v>0.072376</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.936724</v>
+        <v>0.927515</v>
       </c>
       <c r="AM9" t="n">
-        <v>-6.33</v>
+        <v>-7.25</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
@@ -6303,10 +5823,10 @@
         <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.055302</v>
+        <v>0.055137</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.2905</v>
+        <v>1.3127</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
@@ -6458,7 +5978,7 @@
         <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.5464</v>
+        <v>0.5491</v>
       </c>
       <c r="CQ9" t="n">
         <v>0</v>
@@ -6585,13 +6105,13 @@
         <v>0.2834</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.015</v>
+        <v>0.0152</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.4858</v>
+        <v>0.5019</v>
       </c>
       <c r="AH10" t="n">
-        <v>13.52</v>
+        <v>13.49</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -6600,13 +6120,13 @@
         <v>0.0076</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.003912</v>
+        <v>0.002782</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.97655</v>
+        <v>0.9737</v>
       </c>
       <c r="AM10" t="n">
-        <v>-2.34</v>
+        <v>-2.63</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
@@ -6636,10 +6156,10 @@
         <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.041743</v>
+        <v>0.042411</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="AY10" t="n">
         <v>0</v>
@@ -6791,7 +6311,7 @@
         <v>1</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.4081</v>
+        <v>0.4021</v>
       </c>
       <c r="CQ10" t="n">
         <v>0</v>
@@ -6918,13 +6438,13 @@
         <v>0.165</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0165</v>
+        <v>0.0169</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.3931</v>
+        <v>0.4194</v>
       </c>
       <c r="AH11" t="n">
-        <v>24.9</v>
+        <v>24.79</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -6933,13 +6453,13 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.149313</v>
+        <v>0.141904</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.8941519999999999</v>
+        <v>0.8465510000000001</v>
       </c>
       <c r="AM11" t="n">
-        <v>-10.58</v>
+        <v>-15.34</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
@@ -6969,10 +6489,10 @@
         <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.045913</v>
+        <v>0.047054</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.2521</v>
+        <v>3.0158</v>
       </c>
       <c r="AY11" t="n">
         <v>1</v>
@@ -7124,7 +6644,7 @@
         <v>0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.5735</v>
+        <v>0.5682</v>
       </c>
       <c r="CQ11" t="n">
         <v>0</v>
@@ -7255,13 +6775,13 @@
         <v>-0.0561</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0266</v>
+        <v>0.0256</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.3588</v>
+        <v>0.3189</v>
       </c>
       <c r="AH12" t="n">
-        <v>8.26</v>
+        <v>8.32</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -7270,22 +6790,22 @@
         <v>-0.0072</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.016831</v>
+        <v>0.025759</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.12131</v>
+        <v>1.153894</v>
       </c>
       <c r="AM12" t="n">
-        <v>12.13</v>
+        <v>15.39</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ12" t="n">
         <v>0</v>
@@ -7306,10 +6826,10 @@
         <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.074368</v>
+        <v>0.071451</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.2263</v>
+        <v>0.3605</v>
       </c>
       <c r="AY12" t="n">
         <v>0</v>
@@ -7324,7 +6844,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>expansao</t>
         </is>
       </c>
       <c r="BC12" t="n">
@@ -7461,7 +6981,7 @@
         <v>0</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.4507</v>
+        <v>0.4721</v>
       </c>
       <c r="CQ12" t="n">
         <v>0</v>
@@ -7592,13 +7112,13 @@
         <v>-0.008</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0233</v>
+        <v>0.0238</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.3883</v>
+        <v>0.4117</v>
       </c>
       <c r="AH13" t="n">
-        <v>13.41</v>
+        <v>13.36</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -7607,13 +7127,13 @@
         <v>-0.0038</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.022653</v>
+        <v>-0.023389</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.998602</v>
+        <v>0.9968089999999999</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0.14</v>
+        <v>-0.32</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
@@ -7643,10 +7163,10 @@
         <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.06496300000000001</v>
+        <v>0.066291</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.3487</v>
+        <v>0.3528</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
@@ -7794,7 +7314,7 @@
         <v>0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.4851</v>
+        <v>0.4809</v>
       </c>
       <c r="CQ13" t="n">
         <v>0</v>
@@ -7921,13 +7441,13 @@
         <v>0.0311</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0142</v>
+        <v>0.0145</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.5749</v>
+        <v>0.5918</v>
       </c>
       <c r="AH14" t="n">
-        <v>41.18</v>
+        <v>40.92</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -7936,13 +7456,13 @@
         <v>0.008</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.022285</v>
+        <v>0.021715</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.982198</v>
+        <v>0.983479</v>
       </c>
       <c r="AM14" t="n">
-        <v>-1.78</v>
+        <v>-1.65</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
@@ -7972,10 +7492,10 @@
         <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.039755</v>
+        <v>0.040382</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.5606</v>
+        <v>0.5377</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
@@ -8123,7 +7643,7 @@
         <v>0</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.3065</v>
+        <v>0.3008</v>
       </c>
       <c r="CQ14" t="n">
         <v>0</v>
@@ -8250,13 +7770,13 @@
         <v>0.3815</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.0369</v>
+        <v>0.0368</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.2104</v>
+        <v>0.2096</v>
       </c>
       <c r="AH15" t="n">
-        <v>10.49</v>
+        <v>10.55</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -8265,13 +7785,13 @@
         <v>0.3823</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0.07579</v>
+        <v>-0.070178</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.038626</v>
+        <v>1.068375</v>
       </c>
       <c r="AM15" t="n">
-        <v>3.86</v>
+        <v>6.84</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
@@ -8301,10 +7821,10 @@
         <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.1029</v>
+        <v>0.10264</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.7365</v>
+        <v>0.6837</v>
       </c>
       <c r="AY15" t="n">
         <v>0</v>
@@ -8456,7 +7976,7 @@
         <v>1</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.5122</v>
+        <v>0.507</v>
       </c>
       <c r="CQ15" t="n">
         <v>0</v>
@@ -8587,13 +8107,13 @@
         <v>-0.1003</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0278</v>
+        <v>0.0276</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.2967</v>
+        <v>0.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.57</v>
+        <v>4.59</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -8602,13 +8122,13 @@
         <v>-0.0147</v>
       </c>
       <c r="AK16" t="n">
-        <v>-0.021621</v>
+        <v>-0.018698</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.082745</v>
+        <v>1.126444</v>
       </c>
       <c r="AM16" t="n">
-        <v>8.27</v>
+        <v>12.64</v>
       </c>
       <c r="AN16" t="n">
         <v>1</v>
@@ -8638,10 +8158,10 @@
         <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.07756200000000001</v>
+        <v>0.077044</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.2788</v>
+        <v>0.2427</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
@@ -8793,7 +8313,7 @@
         <v>1</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.4701</v>
+        <v>0.4679</v>
       </c>
       <c r="CQ16" t="n">
         <v>0</v>
@@ -8848,7 +8368,7 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -8924,13 +8444,13 @@
         <v>-0.0331</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0128</v>
+        <v>0.0132</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.0806</v>
+        <v>0.0919</v>
       </c>
       <c r="AH17" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -8939,13 +8459,13 @@
         <v>0.0066</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.025491</v>
+        <v>0.0215</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.231796</v>
+        <v>1.242259</v>
       </c>
       <c r="AM17" t="n">
-        <v>23.18</v>
+        <v>24.23</v>
       </c>
       <c r="AN17" t="n">
         <v>1</v>
@@ -8975,10 +8495,10 @@
         <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.035599</v>
+        <v>0.036766</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.716</v>
+        <v>0.5848</v>
       </c>
       <c r="AY17" t="n">
         <v>0</v>
@@ -8988,7 +8508,7 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
@@ -9130,7 +8650,7 @@
         <v>0</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.5047</v>
+        <v>0.4894</v>
       </c>
       <c r="CQ17" t="n">
         <v>0</v>
@@ -9245,13 +8765,13 @@
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="n">
-        <v>0.0395</v>
+        <v>0.0404</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.6129</v>
+        <v>0.6367</v>
       </c>
       <c r="AH18" t="n">
-        <v>5.23</v>
+        <v>5.2</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -9260,13 +8780,13 @@
         <v>-0</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.083161</v>
+        <v>0.078814</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.884536</v>
+        <v>0.873705</v>
       </c>
       <c r="AM18" t="n">
-        <v>-11.55</v>
+        <v>-12.63</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
@@ -9296,10 +8816,10 @@
         <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.110177</v>
+        <v>0.112734</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.7548</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="AY18" t="n">
         <v>0</v>
@@ -9447,7 +8967,7 @@
         <v>1</v>
       </c>
       <c r="CP18" t="n">
-        <v>0.456</v>
+        <v>0.4456</v>
       </c>
       <c r="CQ18" t="n">
         <v>0</v>
@@ -9574,13 +9094,13 @@
         <v>0.2125</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.0131</v>
+        <v>0.0133</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.5279</v>
       </c>
       <c r="AH19" t="n">
-        <v>39.13</v>
+        <v>39.05</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -9589,13 +9109,13 @@
         <v>0.1395</v>
       </c>
       <c r="AK19" t="n">
-        <v>-0.033642</v>
+        <v>-0.03419</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.846634</v>
+        <v>0.833668</v>
       </c>
       <c r="AM19" t="n">
-        <v>-15.34</v>
+        <v>-16.63</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
@@ -9625,10 +9145,10 @@
         <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.03643</v>
+        <v>0.037003</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.9235</v>
+        <v>0.924</v>
       </c>
       <c r="AY19" t="n">
         <v>0</v>
@@ -9776,7 +9296,7 @@
         <v>0</v>
       </c>
       <c r="CP19" t="n">
-        <v>0.4524</v>
+        <v>0.4496</v>
       </c>
       <c r="CQ19" t="n">
         <v>0</v>
@@ -9903,13 +9423,13 @@
         <v>0.1336</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.0233</v>
+        <v>0.0229</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.2522</v>
+        <v>0.2442</v>
       </c>
       <c r="AH20" t="n">
-        <v>20.68</v>
+        <v>20.77</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -9918,13 +9438,13 @@
         <v>0.0217</v>
       </c>
       <c r="AK20" t="n">
-        <v>-0.060325</v>
+        <v>-0.054032</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.9791069999999999</v>
+        <v>0.9802070000000001</v>
       </c>
       <c r="AM20" t="n">
-        <v>-2.09</v>
+        <v>-1.98</v>
       </c>
       <c r="AN20" t="n">
         <v>0</v>
@@ -9954,10 +9474,10 @@
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.06498900000000001</v>
+        <v>0.06386600000000001</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.9282</v>
+        <v>0.846</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
@@ -9972,7 +9492,7 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>compressao</t>
+          <t>neutro_zona_cinza</t>
         </is>
       </c>
       <c r="BC20" t="n">
@@ -10109,7 +9629,7 @@
         <v>0</v>
       </c>
       <c r="CP20" t="n">
-        <v>0.4936</v>
+        <v>0.487</v>
       </c>
       <c r="CQ20" t="n">
         <v>0</v>
@@ -10240,13 +9760,13 @@
         <v>0.0421</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.0188</v>
+        <v>0.019</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.1084</v>
+        <v>0.1122</v>
       </c>
       <c r="AH21" t="n">
-        <v>17.79</v>
+        <v>17.76</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -10255,13 +9775,13 @@
         <v>0.0114</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.026684</v>
+        <v>0.026003</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.08536</v>
+        <v>1.082551</v>
       </c>
       <c r="AM21" t="n">
-        <v>8.539999999999999</v>
+        <v>8.26</v>
       </c>
       <c r="AN21" t="n">
         <v>0</v>
@@ -10291,10 +9811,10 @@
         <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.052567</v>
+        <v>0.053061</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.4901</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
@@ -10446,7 +9966,7 @@
         <v>1</v>
       </c>
       <c r="CP21" t="n">
-        <v>0.5029</v>
+        <v>0.5004</v>
       </c>
       <c r="CQ21" t="n">
         <v>0</v>
@@ -10573,13 +10093,13 @@
         <v>0.1537</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.0237</v>
+        <v>0.024</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.3606</v>
+        <v>0.3704</v>
       </c>
       <c r="AH22" t="n">
-        <v>10.6</v>
+        <v>10.58</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -10588,22 +10108,22 @@
         <v>0.0527</v>
       </c>
       <c r="AK22" t="n">
-        <v>-0.015945</v>
+        <v>-0.016686</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.159498</v>
+        <v>1.091831</v>
       </c>
       <c r="AM22" t="n">
-        <v>15.95</v>
+        <v>9.18</v>
       </c>
       <c r="AN22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
         <v>0</v>
@@ -10624,10 +10144,10 @@
         <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.066188</v>
+        <v>0.066939</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.2409</v>
+        <v>0.2493</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
@@ -10642,7 +10162,7 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>expansao</t>
+          <t>neutro_zona_cinza</t>
         </is>
       </c>
       <c r="BC22" t="n">
@@ -10775,7 +10295,7 @@
         <v>0</v>
       </c>
       <c r="CP22" t="n">
-        <v>0.3904</v>
+        <v>0.3892</v>
       </c>
       <c r="CQ22" t="n">
         <v>0</v>
@@ -10876,7 +10396,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
+          <t>spread_35_20,spread_45_15,spread_45_25</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10906,13 +10426,13 @@
         <v>-0.0545</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.0216</v>
+        <v>0.0233</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.5353</v>
+        <v>0.6098</v>
       </c>
       <c r="AH23" t="n">
-        <v>26.87</v>
+        <v>26.61</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -10921,13 +10441,13 @@
         <v>-0.0174</v>
       </c>
       <c r="AK23" t="n">
-        <v>-0.066098</v>
+        <v>-0.06830700000000001</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.971697</v>
+        <v>0.932344</v>
       </c>
       <c r="AM23" t="n">
-        <v>-2.83</v>
+        <v>-6.77</v>
       </c>
       <c r="AN23" t="n">
         <v>0</v>
@@ -10957,10 +10477,10 @@
         <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.06021</v>
+        <v>0.065109</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.0978</v>
+        <v>1.0491</v>
       </c>
       <c r="AY23" t="n">
         <v>0</v>
@@ -11112,7 +10632,7 @@
         <v>1</v>
       </c>
       <c r="CP23" t="n">
-        <v>0.5104</v>
+        <v>0.4906</v>
       </c>
       <c r="CQ23" t="n">
         <v>0</v>
@@ -11150,7 +10670,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11159,19 +10679,15 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -11184,7 +10700,7 @@
         <v>0.7193000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3793</v>
+        <v>0.3826</v>
       </c>
       <c r="N24" t="n">
         <v>0.7677</v>
@@ -11208,7 +10724,7 @@
         <v>0.1909</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0518</v>
+        <v>0.052</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -11252,25 +10768,25 @@
         <v>10.77</v>
       </c>
       <c r="AI24" t="n">
-        <v>11.17</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
         <v>0.0476</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.118415</v>
+        <v>0.120429</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.128108</v>
+        <v>1.114427</v>
       </c>
       <c r="AM24" t="n">
-        <v>12.81</v>
+        <v>11.44</v>
       </c>
       <c r="AN24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP24" t="n">
         <v>0</v>
@@ -11291,13 +10807,13 @@
         <v>1</v>
       </c>
       <c r="AV24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
         <v>0.044087</v>
       </c>
       <c r="AX24" t="n">
-        <v>2.686</v>
+        <v>2.7316</v>
       </c>
       <c r="AY24" t="n">
         <v>0</v>
@@ -11452,68 +10968,24 @@
         <v>0.5923</v>
       </c>
       <c r="CQ24" t="n">
-        <v>0.5923</v>
-      </c>
-      <c r="CR24" t="inlineStr">
-        <is>
-          <t>Call delta~45 naked (quase ATM, ~0.9σ, 20d)</t>
-        </is>
-      </c>
-      <c r="CS24" t="inlineStr">
-        <is>
-          <t>Call delta~50 naked (ATM, máximo gamma)</t>
-        </is>
-      </c>
-      <c r="CT24" t="inlineStr">
-        <is>
-          <t>Call delta~40 naked (ligeiramente mais OTM)</t>
-        </is>
-      </c>
-      <c r="CU24" t="inlineStr">
-        <is>
-          <t>OTM extremo (&lt;delta~20) sem vol prevista muito forte</t>
-        </is>
-      </c>
-      <c r="CV24" t="inlineStr">
-        <is>
-          <t>~0.45</t>
-        </is>
-      </c>
-      <c r="CW24" t="inlineStr">
-        <is>
-          <t>naked_30: esp=+0.190 | spread_35_20: esp=+0.067 | spread_45_25: esp=+0.078 | spread_45_15: esp=+0.130</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="CR24" t="inlineStr"/>
+      <c r="CS24" t="inlineStr"/>
+      <c r="CT24" t="inlineStr"/>
+      <c r="CU24" t="inlineStr"/>
+      <c r="CV24" t="inlineStr"/>
+      <c r="CW24" t="inlineStr"/>
       <c r="CX24" t="inlineStr">
         <is>
-          <t>[Empírico] Call delta~45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.259 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
-        </is>
-      </c>
-      <c r="CY24" t="inlineStr">
-        <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="CZ24" t="inlineStr">
-        <is>
-          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.053%/dia | carry 20 pregões: 1.06%]</t>
-        </is>
-      </c>
-      <c r="DA24" t="inlineStr">
-        <is>
-          <t>100% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="DB24" t="inlineStr">
-        <is>
-          <t>50% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="DC24" t="inlineStr">
-        <is>
-          <t>Edge forte — aguardar dobrar o prêmio. Stop 50%.</t>
-        </is>
-      </c>
+          <t>Ticker neutro — sem sinal operacional</t>
+        </is>
+      </c>
+      <c r="CY24" t="inlineStr"/>
+      <c r="CZ24" t="inlineStr"/>
+      <c r="DA24" t="inlineStr"/>
+      <c r="DB24" t="inlineStr"/>
+      <c r="DC24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11624,13 +11096,13 @@
         <v>0.0626</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.0193</v>
+        <v>0.0196</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.6473</v>
+        <v>0.6676</v>
       </c>
       <c r="AH25" t="n">
-        <v>29.41</v>
+        <v>29.29</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -11639,13 +11111,13 @@
         <v>0.0061</v>
       </c>
       <c r="AK25" t="n">
-        <v>-0.01272</v>
+        <v>-0.013734</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.940334</v>
+        <v>0.951523</v>
       </c>
       <c r="AM25" t="n">
-        <v>-5.97</v>
+        <v>-4.85</v>
       </c>
       <c r="AN25" t="n">
         <v>0</v>
@@ -11675,10 +11147,10 @@
         <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.053734</v>
+        <v>0.054607</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.2367</v>
+        <v>0.2515</v>
       </c>
       <c r="AY25" t="n">
         <v>0</v>
@@ -11830,7 +11302,7 @@
         <v>1</v>
       </c>
       <c r="CP25" t="n">
-        <v>0.3908</v>
+        <v>0.3882</v>
       </c>
       <c r="CQ25" t="n">
         <v>0</v>
@@ -11957,13 +11429,13 @@
         <v>0.139</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.0163</v>
+        <v>0.0164</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.5292</v>
       </c>
       <c r="AH26" t="n">
-        <v>21.69</v>
+        <v>21.66</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -11972,13 +11444,13 @@
         <v>0.1662</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.022114</v>
+        <v>0.021987</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.971884</v>
+        <v>0.975306</v>
       </c>
       <c r="AM26" t="n">
-        <v>-2.81</v>
+        <v>-2.47</v>
       </c>
       <c r="AN26" t="n">
         <v>0</v>
@@ -12008,10 +11480,10 @@
         <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.045573</v>
+        <v>0.045657</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.4852</v>
+        <v>0.4816</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
@@ -12163,7 +11635,7 @@
         <v>0</v>
       </c>
       <c r="CP26" t="n">
-        <v>0.4112</v>
+        <v>0.4106</v>
       </c>
       <c r="CQ26" t="n">
         <v>0</v>
@@ -12218,7 +11690,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -12294,13 +11766,13 @@
         <v>-0.222</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.0379</v>
+        <v>0.0383</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.2305</v>
+        <v>0.2372</v>
       </c>
       <c r="AH27" t="n">
-        <v>6.08</v>
+        <v>5.72</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -12309,19 +11781,19 @@
         <v>-0.008999999999999999</v>
       </c>
       <c r="AK27" t="n">
-        <v>-0.020195</v>
+        <v>-0.075169</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.004003</v>
+        <v>1.096704</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.4</v>
+        <v>9.67</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP27" t="n">
         <v>0</v>
@@ -12345,10 +11817,10 @@
         <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.105708</v>
+        <v>0.107019</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.191</v>
+        <v>0.7024</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -12358,7 +11830,7 @@
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
@@ -12496,7 +11968,7 @@
         <v>0</v>
       </c>
       <c r="CP27" t="n">
-        <v>0.4437</v>
+        <v>0.4935</v>
       </c>
       <c r="CQ27" t="n">
         <v>0</v>
@@ -12627,13 +12099,13 @@
         <v>0.0243</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.0266</v>
+        <v>0.0263</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.6172</v>
+        <v>0.6085</v>
       </c>
       <c r="AH28" t="n">
-        <v>11.07</v>
+        <v>11.09</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -12642,13 +12114,13 @@
         <v>0.0164</v>
       </c>
       <c r="AK28" t="n">
-        <v>-0.115684</v>
+        <v>-0.113876</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.085961</v>
+        <v>1.087916</v>
       </c>
       <c r="AM28" t="n">
-        <v>8.6</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="AN28" t="n">
         <v>0</v>
@@ -12678,10 +12150,10 @@
         <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.07413400000000001</v>
+        <v>0.07349600000000001</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.5605</v>
+        <v>1.5494</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
@@ -12829,7 +12301,7 @@
         <v>0</v>
       </c>
       <c r="CP28" t="n">
-        <v>0.481</v>
+        <v>0.4816</v>
       </c>
       <c r="CQ28" t="n">
         <v>0</v>
@@ -12960,13 +12432,13 @@
         <v>-0.06850000000000001</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.0204</v>
+        <v>0.0208</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.2094</v>
+        <v>0.2229</v>
       </c>
       <c r="AH29" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -12975,13 +12447,13 @@
         <v>-0.0028</v>
       </c>
       <c r="AK29" t="n">
-        <v>-0.015583</v>
+        <v>-0.012323</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.107826</v>
+        <v>1.094684</v>
       </c>
       <c r="AM29" t="n">
-        <v>10.78</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="AN29" t="n">
         <v>0</v>
@@ -13011,10 +12483,10 @@
         <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.056928</v>
+        <v>0.058169</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.2737</v>
+        <v>0.2118</v>
       </c>
       <c r="AY29" t="n">
         <v>0</v>
@@ -13162,7 +12634,7 @@
         <v>0</v>
       </c>
       <c r="CP29" t="n">
-        <v>0.4713</v>
+        <v>0.4624</v>
       </c>
       <c r="CQ29" t="n">
         <v>0</v>
@@ -13289,13 +12761,13 @@
         <v>0.1138</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.0185</v>
+        <v>0.0186</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.3169</v>
+        <v>0.3226</v>
       </c>
       <c r="AH30" t="n">
-        <v>5.33</v>
+        <v>5.31</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -13304,13 +12776,13 @@
         <v>0.0407</v>
       </c>
       <c r="AK30" t="n">
-        <v>-0.036524</v>
+        <v>-0.038049</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.102425</v>
+        <v>1.099592</v>
       </c>
       <c r="AM30" t="n">
-        <v>10.24</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="AN30" t="n">
         <v>1</v>
@@ -13340,10 +12812,10 @@
         <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.051526</v>
+        <v>0.051978</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.7088</v>
+        <v>0.732</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
@@ -13495,7 +12967,7 @@
         <v>1</v>
       </c>
       <c r="CP30" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.5188</v>
       </c>
       <c r="CQ30" t="n">
         <v>0</v>
@@ -13626,13 +13098,13 @@
         <v>0.0533</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.0181</v>
+        <v>0.0188</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.4831</v>
+        <v>0.5245</v>
       </c>
       <c r="AH31" t="n">
-        <v>14.63</v>
+        <v>14.53</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -13641,13 +13113,13 @@
         <v>0.0451</v>
       </c>
       <c r="AK31" t="n">
-        <v>-0.011322</v>
+        <v>-0.014719</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.120376</v>
+        <v>1.116047</v>
       </c>
       <c r="AM31" t="n">
-        <v>12.04</v>
+        <v>11.6</v>
       </c>
       <c r="AN31" t="n">
         <v>1</v>
@@ -13677,10 +13149,10 @@
         <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.050394</v>
+        <v>0.052416</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.2247</v>
+        <v>0.2808</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
@@ -13828,7 +13300,7 @@
         <v>0</v>
       </c>
       <c r="CP31" t="n">
-        <v>0.3546</v>
+        <v>0.352</v>
       </c>
       <c r="CQ31" t="n">
         <v>0</v>
@@ -13903,7 +13375,7 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>0.2667</v>
+        <v>0.2666</v>
       </c>
       <c r="O32" t="n">
         <v>-0.18</v>
@@ -13966,22 +13438,22 @@
         <v>0.0106</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.1902</v>
+        <v>0.1926</v>
       </c>
       <c r="AH32" t="n">
-        <v>18.04</v>
+        <v>18.02</v>
       </c>
       <c r="AI32" t="n">
-        <v>18.48</v>
+        <v>18.46</v>
       </c>
       <c r="AJ32" t="n">
         <v>-0.0127</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.042047</v>
+        <v>0.041081</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.17222</v>
+        <v>1.172216</v>
       </c>
       <c r="AM32" t="n">
         <v>17.22</v>
@@ -14014,10 +13486,10 @@
         <v>1</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.029493</v>
+        <v>0.029586</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.4256</v>
+        <v>1.3885</v>
       </c>
       <c r="AY32" t="n">
         <v>0</v>
@@ -14165,10 +13637,10 @@
         <v>0</v>
       </c>
       <c r="CP32" t="n">
-        <v>0.5564</v>
+        <v>0.5522</v>
       </c>
       <c r="CQ32" t="n">
-        <v>0.5564</v>
+        <v>0.5522</v>
       </c>
       <c r="CR32" t="inlineStr">
         <is>
@@ -14251,7 +13723,7 @@
         <v>1.4798</v>
       </c>
       <c r="O33" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.5298</v>
       </c>
       <c r="P33" t="n">
         <v>0.1278</v>
@@ -14304,13 +13776,13 @@
         <v>0.0979</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.0173</v>
+        <v>0.0168</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.417</v>
+        <v>0.3932</v>
       </c>
       <c r="AH33" t="n">
-        <v>26.46</v>
+        <v>26.58</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -14319,13 +13791,13 @@
         <v>0.0106</v>
       </c>
       <c r="AK33" t="n">
-        <v>-0.022997</v>
+        <v>-0.021769</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.874369</v>
+        <v>0.898048</v>
       </c>
       <c r="AM33" t="n">
-        <v>-12.56</v>
+        <v>-10.2</v>
       </c>
       <c r="AN33" t="n">
         <v>0</v>
@@ -14355,10 +13827,10 @@
         <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.048179</v>
+        <v>0.04679</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.4773</v>
+        <v>0.4653</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
@@ -14510,7 +13982,7 @@
         <v>1</v>
       </c>
       <c r="CP33" t="n">
-        <v>0.4282</v>
+        <v>0.4318</v>
       </c>
       <c r="CQ33" t="n">
         <v>0</v>
@@ -14581,10 +14053,10 @@
         <v>0.3333</v>
       </c>
       <c r="N34" t="n">
-        <v>2.2054</v>
+        <v>2.202</v>
       </c>
       <c r="O34" t="n">
-        <v>2.3074</v>
+        <v>2.294</v>
       </c>
       <c r="P34" t="n">
         <v>-0.1484</v>
@@ -14599,10 +14071,10 @@
         <v>295</v>
       </c>
       <c r="T34" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.6485</v>
       </c>
       <c r="U34" t="n">
-        <v>0.2414</v>
+        <v>0.2411</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -14616,16 +14088,16 @@
       </c>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="n">
-        <v>0.6488</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.0276</v>
+        <v>2.024</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.6475</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.6488</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="AC34" t="n">
         <v>0.0313</v>
@@ -14637,28 +14109,28 @@
         <v>0.0474</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.0195</v>
+        <v>0.0196</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.4054</v>
+        <v>0.4118</v>
       </c>
       <c r="AH34" t="n">
-        <v>32.05</v>
+        <v>32</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.0327</v>
+        <v>0.0326</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.07681</v>
+        <v>0.07657600000000001</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.700828</v>
+        <v>0.711456</v>
       </c>
       <c r="AM34" t="n">
-        <v>-29.92</v>
+        <v>-28.85</v>
       </c>
       <c r="AN34" t="n">
         <v>0</v>
@@ -14688,10 +14160,10 @@
         <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.054447</v>
+        <v>0.054806</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.4107</v>
+        <v>1.3972</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
@@ -14839,7 +14311,7 @@
         <v>0</v>
       </c>
       <c r="CP34" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="CQ34" t="n">
         <v>0</v>
@@ -14985,13 +14457,13 @@
         <v>-0.007900000000000001</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.018183</v>
+        <v>0.0178</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.931104</v>
+        <v>0.97578</v>
       </c>
       <c r="AM35" t="n">
-        <v>-6.89</v>
+        <v>-2.42</v>
       </c>
       <c r="AN35" t="n">
         <v>0</v>
@@ -15003,7 +14475,7 @@
         <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
         <v>1.034102</v>
@@ -15024,7 +14496,7 @@
         <v>0.061669</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.2949</v>
+        <v>0.2886</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
@@ -15172,7 +14644,7 @@
         <v>0</v>
       </c>
       <c r="CP35" t="n">
-        <v>0.415</v>
+        <v>0.4144</v>
       </c>
       <c r="CQ35" t="n">
         <v>0</v>
@@ -15299,13 +14771,13 @@
         <v>0.0833</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.0197</v>
+        <v>0.0201</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.5712</v>
+        <v>0.589</v>
       </c>
       <c r="AH36" t="n">
-        <v>27.6</v>
+        <v>27.54</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -15314,13 +14786,13 @@
         <v>0.0114</v>
       </c>
       <c r="AK36" t="n">
-        <v>-0.030675</v>
+        <v>-0.030999</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.904258</v>
+        <v>0.897088</v>
       </c>
       <c r="AM36" t="n">
-        <v>-9.57</v>
+        <v>-10.29</v>
       </c>
       <c r="AN36" t="n">
         <v>0</v>
@@ -15350,10 +14822,10 @@
         <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.055107</v>
+        <v>0.056137</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.5566</v>
+        <v>0.5522</v>
       </c>
       <c r="AY36" t="n">
         <v>0</v>
@@ -15505,7 +14977,7 @@
         <v>0</v>
       </c>
       <c r="CP36" t="n">
-        <v>0.3921</v>
+        <v>0.3881</v>
       </c>
       <c r="CQ36" t="n">
         <v>0</v>
@@ -15594,7 +15066,7 @@
         <v>276</v>
       </c>
       <c r="T37" t="n">
-        <v>0.3336</v>
+        <v>0.3337</v>
       </c>
       <c r="U37" t="n">
         <v>0.1252</v>
@@ -15617,7 +15089,7 @@
         <v>1.307</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.3326</v>
+        <v>0.3327</v>
       </c>
       <c r="AB37" t="n">
         <v>0.4182</v>
@@ -15632,13 +15104,13 @@
         <v>0.1978</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.0243</v>
+        <v>0.0227</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.4007</v>
+        <v>0.3579</v>
       </c>
       <c r="AH37" t="n">
-        <v>61.21</v>
+        <v>61.82</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -15647,13 +15119,13 @@
         <v>0.0161</v>
       </c>
       <c r="AK37" t="n">
-        <v>-0.010101</v>
+        <v>-0.004256</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.643989</v>
+        <v>0.68443</v>
       </c>
       <c r="AM37" t="n">
-        <v>-35.6</v>
+        <v>-31.56</v>
       </c>
       <c r="AN37" t="n">
         <v>0</v>
@@ -15683,10 +15155,10 @@
         <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.067881</v>
+        <v>0.06346</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.1488</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="AY37" t="n">
         <v>0</v>
@@ -15834,7 +15306,7 @@
         <v>0</v>
       </c>
       <c r="CP37" t="n">
-        <v>0.4123</v>
+        <v>0.4127</v>
       </c>
       <c r="CQ37" t="n">
         <v>0</v>
@@ -15964,10 +15436,10 @@
         <v>0.0271</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.2376</v>
+        <v>0.2374</v>
       </c>
       <c r="AH38" t="n">
-        <v>8.16</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -15976,13 +15448,13 @@
         <v>0.0095</v>
       </c>
       <c r="AK38" t="n">
-        <v>-0.027055</v>
+        <v>-0.02789</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.113619</v>
+        <v>1.149098</v>
       </c>
       <c r="AM38" t="n">
-        <v>11.36</v>
+        <v>14.91</v>
       </c>
       <c r="AN38" t="n">
         <v>1</v>
@@ -16012,10 +15484,10 @@
         <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.07568999999999999</v>
+        <v>0.07567699999999999</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.3574</v>
+        <v>0.3685</v>
       </c>
       <c r="AY38" t="n">
         <v>0</v>
@@ -16167,7 +15639,7 @@
         <v>1</v>
       </c>
       <c r="CP38" t="n">
-        <v>0.4818</v>
+        <v>0.483</v>
       </c>
       <c r="CQ38" t="n">
         <v>0</v>
@@ -16294,13 +15766,13 @@
         <v>0.0412</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.0149</v>
+        <v>0.0148</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.5162</v>
+        <v>0.5147</v>
       </c>
       <c r="AH39" t="n">
-        <v>13.07</v>
+        <v>13.09</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -16309,13 +15781,13 @@
         <v>0.0247</v>
       </c>
       <c r="AK39" t="n">
-        <v>-0.002998</v>
+        <v>-0.001225</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.15442</v>
+        <v>1.171809</v>
       </c>
       <c r="AM39" t="n">
-        <v>15.44</v>
+        <v>17.18</v>
       </c>
       <c r="AN39" t="n">
         <v>0</v>
@@ -16345,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.041508</v>
+        <v>0.041436</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.0722</v>
+        <v>0.0296</v>
       </c>
       <c r="AY39" t="n">
         <v>0</v>
@@ -16500,7 +15972,7 @@
         <v>0</v>
       </c>
       <c r="CP39" t="n">
-        <v>0.3844</v>
+        <v>0.3804</v>
       </c>
       <c r="CQ39" t="n">
         <v>0</v>
@@ -16631,13 +16103,13 @@
         <v>-0.014</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.0244</v>
+        <v>0.0247</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.8587</v>
+        <v>0.8736</v>
       </c>
       <c r="AH40" t="n">
-        <v>26.46</v>
+        <v>26.29</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -16646,13 +16118,13 @@
         <v>0.0107</v>
       </c>
       <c r="AK40" t="n">
-        <v>-0.000534</v>
+        <v>-0.001392</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.875564</v>
+        <v>0.8780019999999999</v>
       </c>
       <c r="AM40" t="n">
-        <v>-12.44</v>
+        <v>-12.2</v>
       </c>
       <c r="AN40" t="n">
         <v>0</v>
@@ -16682,10 +16154,10 @@
         <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.067994</v>
+        <v>0.068824</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0202</v>
       </c>
       <c r="AY40" t="n">
         <v>0</v>
@@ -16833,7 +16305,7 @@
         <v>0</v>
       </c>
       <c r="CP40" t="n">
-        <v>0.3134</v>
+        <v>0.3116</v>
       </c>
       <c r="CQ40" t="n">
         <v>0</v>
@@ -16964,13 +16436,13 @@
         <v>-0.08119999999999999</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.0164</v>
+        <v>0.0162</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.389</v>
+        <v>0.3811</v>
       </c>
       <c r="AH41" t="n">
-        <v>14.15</v>
+        <v>14.16</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -16979,13 +16451,13 @@
         <v>0.0026</v>
       </c>
       <c r="AK41" t="n">
-        <v>-0.005681</v>
+        <v>-0.006102</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.053327</v>
+        <v>1.058002</v>
       </c>
       <c r="AM41" t="n">
-        <v>5.33</v>
+        <v>5.8</v>
       </c>
       <c r="AN41" t="n">
         <v>0</v>
@@ -17015,10 +16487,10 @@
         <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.045642</v>
+        <v>0.045283</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.1245</v>
+        <v>0.1347</v>
       </c>
       <c r="AY41" t="n">
         <v>0</v>
@@ -17170,7 +16642,7 @@
         <v>1</v>
       </c>
       <c r="CP41" t="n">
-        <v>0.4546</v>
+        <v>0.4572</v>
       </c>
       <c r="CQ41" t="n">
         <v>0</v>
@@ -17295,19 +16767,19 @@
         <v>-0.0355</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.0566</v>
+        <v>-0.0567</v>
       </c>
       <c r="AE42" t="n">
         <v>-0.0664</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.0173</v>
+        <v>0.0167</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.4852</v>
       </c>
       <c r="AH42" t="n">
-        <v>53.56</v>
+        <v>53.81</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -17316,13 +16788,13 @@
         <v>0.0056</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.004044</v>
+        <v>0.006194</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.015294</v>
+        <v>1.024101</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.53</v>
+        <v>2.41</v>
       </c>
       <c r="AN42" t="n">
         <v>0</v>
@@ -17352,10 +16824,10 @@
         <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.048192</v>
+        <v>0.046681</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.0839</v>
+        <v>0.1327</v>
       </c>
       <c r="AY42" t="n">
         <v>0</v>
@@ -17507,7 +16979,7 @@
         <v>0</v>
       </c>
       <c r="CP42" t="n">
-        <v>0.3999</v>
+        <v>0.4118</v>
       </c>
       <c r="CQ42" t="n">
         <v>0</v>
@@ -17582,7 +17054,7 @@
         <v>0.4516</v>
       </c>
       <c r="N43" t="n">
-        <v>1.2835</v>
+        <v>1.2856</v>
       </c>
       <c r="O43" t="n">
         <v>0.7368</v>
@@ -17600,10 +17072,10 @@
         <v>379</v>
       </c>
       <c r="T43" t="n">
-        <v>0.6643</v>
+        <v>0.6655</v>
       </c>
       <c r="U43" t="n">
-        <v>0.117</v>
+        <v>0.1171</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -17617,16 +17089,16 @@
       </c>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="n">
-        <v>0.8399</v>
+        <v>0.8411</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.6248</v>
+        <v>2.6285</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.6633</v>
+        <v>0.6645</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.8399</v>
+        <v>0.8411</v>
       </c>
       <c r="AC43" t="n">
         <v>0.166</v>
@@ -17638,28 +17110,28 @@
         <v>0.331</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.0378</v>
+        <v>0.0381</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.1881</v>
+        <v>0.1929</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.0698</v>
+        <v>0.0699</v>
       </c>
       <c r="AK43" t="n">
-        <v>-0.208582</v>
+        <v>-0.2154</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.181753</v>
+        <v>1.201075</v>
       </c>
       <c r="AM43" t="n">
-        <v>18.18</v>
+        <v>20.11</v>
       </c>
       <c r="AN43" t="n">
         <v>1</v>
@@ -17689,10 +17161,10 @@
         <v>-1</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.105469</v>
+        <v>0.106458</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.9777</v>
+        <v>2.0233</v>
       </c>
       <c r="AY43" t="n">
         <v>0</v>
@@ -17840,10 +17312,10 @@
         <v>1</v>
       </c>
       <c r="CP43" t="n">
-        <v>0.6371</v>
+        <v>0.6384</v>
       </c>
       <c r="CQ43" t="n">
-        <v>0.6371</v>
+        <v>0.6384</v>
       </c>
       <c r="CR43" t="inlineStr">
         <is>
@@ -17872,12 +17344,12 @@
       </c>
       <c r="CW43" t="inlineStr">
         <is>
-          <t>naked_30: esp=+0.663 | spread_35_20: esp=+0.166 | spread_45_25: esp=+0.214 | spread_45_15: esp=+0.331</t>
+          <t>naked_30: esp=+0.664 | spread_35_20: esp=+0.166 | spread_45_25: esp=+0.214 | spread_45_15: esp=+0.331</t>
         </is>
       </c>
       <c r="CX43" t="inlineStr">
         <is>
-          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.840 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.841 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
         </is>
       </c>
       <c r="CY43" t="inlineStr">
@@ -18011,13 +17483,13 @@
         <v>0.1186</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.0168</v>
+        <v>0.0164</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.2724</v>
+        <v>0.2576</v>
       </c>
       <c r="AH44" t="n">
-        <v>16.76</v>
+        <v>16.83</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -18026,13 +17498,13 @@
         <v>0.0083</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.039666</v>
+        <v>0.042588</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.08893</v>
+        <v>1.108708</v>
       </c>
       <c r="AM44" t="n">
-        <v>8.890000000000001</v>
+        <v>10.87</v>
       </c>
       <c r="AN44" t="n">
         <v>0</v>
@@ -18062,10 +17534,10 @@
         <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.046957</v>
+        <v>0.045777</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.8447</v>
+        <v>0.9303</v>
       </c>
       <c r="AY44" t="n">
         <v>0</v>
@@ -18217,7 +17689,7 @@
         <v>0</v>
       </c>
       <c r="CP44" t="n">
-        <v>0.5161</v>
+        <v>0.5276</v>
       </c>
       <c r="CQ44" t="n">
         <v>0</v>
@@ -18359,13 +17831,13 @@
         <v>0.0059</v>
       </c>
       <c r="AK45" t="n">
-        <v>-0.013911</v>
+        <v>-0.015344</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.242197</v>
+        <v>1.271659</v>
       </c>
       <c r="AM45" t="n">
-        <v>24.22</v>
+        <v>27.17</v>
       </c>
       <c r="AN45" t="n">
         <v>0</v>
@@ -18398,7 +17870,7 @@
         <v>0.06529799999999999</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.213</v>
+        <v>0.235</v>
       </c>
       <c r="AY45" t="n">
         <v>0</v>
@@ -18546,7 +18018,7 @@
         <v>0</v>
       </c>
       <c r="CP45" t="n">
-        <v>0.4445</v>
+        <v>0.4467</v>
       </c>
       <c r="CQ45" t="n">
         <v>0</v>
@@ -18677,13 +18149,13 @@
         <v>-0.0945</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.019</v>
+        <v>0.0195</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.2847</v>
+        <v>0.3098</v>
       </c>
       <c r="AH46" t="n">
-        <v>11.15</v>
+        <v>11.08</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -18692,13 +18164,13 @@
         <v>-0.0075</v>
       </c>
       <c r="AK46" t="n">
-        <v>-0.102347</v>
+        <v>-0.106811</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.169543</v>
+        <v>1.139942</v>
       </c>
       <c r="AM46" t="n">
-        <v>16.95</v>
+        <v>13.99</v>
       </c>
       <c r="AN46" t="n">
         <v>0</v>
@@ -18728,10 +18200,10 @@
         <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.053092</v>
+        <v>0.054372</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.9277</v>
+        <v>1.9644</v>
       </c>
       <c r="AY46" t="n">
         <v>0</v>
@@ -18883,7 +18355,7 @@
         <v>0</v>
       </c>
       <c r="CP46" t="n">
-        <v>0.6135</v>
+        <v>0.6122</v>
       </c>
       <c r="CQ46" t="n">
         <v>0</v>
@@ -19010,13 +18482,13 @@
         <v>0.2225</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.0264</v>
+        <v>0.0261</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.5004</v>
+        <v>0.4884</v>
       </c>
       <c r="AH47" t="n">
-        <v>6.87</v>
+        <v>6.89</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -19025,13 +18497,13 @@
         <v>0.1433</v>
       </c>
       <c r="AK47" t="n">
-        <v>-0.030584</v>
+        <v>-0.02808</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.007473</v>
+        <v>1.011075</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.75</v>
+        <v>1.11</v>
       </c>
       <c r="AN47" t="n">
         <v>0</v>
@@ -19061,10 +18533,10 @@
         <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.073798</v>
+        <v>0.072809</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.4144</v>
+        <v>0.3857</v>
       </c>
       <c r="AY47" t="n">
         <v>0</v>
@@ -19216,7 +18688,7 @@
         <v>0</v>
       </c>
       <c r="CP47" t="n">
-        <v>0.3849</v>
+        <v>0.3845</v>
       </c>
       <c r="CQ47" t="n">
         <v>0</v>
@@ -19347,13 +18819,13 @@
         <v>-0.1585</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.0288</v>
+        <v>0.0282</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.1857</v>
+        <v>0.1668</v>
       </c>
       <c r="AH48" t="n">
-        <v>7.84</v>
+        <v>7.91</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -19362,13 +18834,13 @@
         <v>0.0021</v>
       </c>
       <c r="AK48" t="n">
-        <v>-0.089424</v>
+        <v>-0.07763200000000001</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.108213</v>
+        <v>1.119037</v>
       </c>
       <c r="AM48" t="n">
-        <v>10.82</v>
+        <v>11.9</v>
       </c>
       <c r="AN48" t="n">
         <v>1</v>
@@ -19398,10 +18870,10 @@
         <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>0.080481</v>
+        <v>0.078719</v>
       </c>
       <c r="AX48" t="n">
-        <v>1.1111</v>
+        <v>0.9862</v>
       </c>
       <c r="AY48" t="n">
         <v>0</v>
@@ -19549,7 +19021,7 @@
         <v>0</v>
       </c>
       <c r="CP48" t="n">
-        <v>0.5312</v>
+        <v>0.5224</v>
       </c>
       <c r="CQ48" t="n">
         <v>0</v>
@@ -19678,13 +19150,13 @@
         <v>-0.2552</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.0242</v>
+        <v>0.0244</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.4822</v>
+        <v>0.4929</v>
       </c>
       <c r="AH49" t="n">
-        <v>11.53</v>
+        <v>11.6</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -19693,19 +19165,19 @@
         <v>-0.0004</v>
       </c>
       <c r="AK49" t="n">
-        <v>-0.008311000000000001</v>
+        <v>-0.005579</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.063986</v>
+        <v>1.058534</v>
       </c>
       <c r="AM49" t="n">
-        <v>6.4</v>
+        <v>5.85</v>
       </c>
       <c r="AN49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP49" t="n">
         <v>0</v>
@@ -19729,10 +19201,10 @@
         <v>0</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.06743300000000001</v>
+        <v>0.068178</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.1233</v>
+        <v>0.0818</v>
       </c>
       <c r="AY49" t="n">
         <v>0</v>
@@ -19880,7 +19352,7 @@
         <v>0</v>
       </c>
       <c r="CP49" t="n">
-        <v>0.405</v>
+        <v>0.3987</v>
       </c>
       <c r="CQ49" t="n">
         <v>0</v>
@@ -20007,13 +19479,13 @@
         <v>0.2292</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.015</v>
+        <v>0.0148</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.1579</v>
+        <v>0.1507</v>
       </c>
       <c r="AH50" t="n">
-        <v>13.89</v>
+        <v>13.92</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -20022,13 +19494,13 @@
         <v>0.039</v>
       </c>
       <c r="AK50" t="n">
-        <v>0.002942</v>
+        <v>0.006206</v>
       </c>
       <c r="AL50" t="n">
-        <v>1.089624</v>
+        <v>1.09081</v>
       </c>
       <c r="AM50" t="n">
-        <v>8.960000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="AN50" t="n">
         <v>1</v>
@@ -20058,10 +19530,10 @@
         <v>0</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.041868</v>
+        <v>0.04129</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.0703</v>
+        <v>0.1503</v>
       </c>
       <c r="AY50" t="n">
         <v>0</v>
@@ -20213,7 +19685,7 @@
         <v>0</v>
       </c>
       <c r="CP50" t="n">
-        <v>0.4216</v>
+        <v>0.431</v>
       </c>
       <c r="CQ50" t="n">
         <v>0</v>
@@ -38761,7 +38233,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -39157,7 +38629,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -39409,12 +38881,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -39517,7 +38989,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -40563,7 +40035,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.5854</v>
+        <v>0.589</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -40629,7 +40101,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.5837</v>
+        <v>0.5426</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -40695,7 +40167,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.457</v>
+        <v>0.4532</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -40745,7 +40217,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -40761,7 +40233,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.4484</v>
+        <v>0.4425</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -40770,7 +40242,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>compressao</t>
+          <t>neutro_zona_cinza</t>
         </is>
       </c>
     </row>
@@ -40854,7 +40326,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -40869,15 +40341,15 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.4864</v>
+        <v>0.4692</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -41123,7 +40595,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0.4335</v>
+        <v>0.4107</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -41189,7 +40661,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0.4588</v>
+        <v>0.458</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -41347,7 +40819,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0.5464</v>
+        <v>0.5491</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -41505,7 +40977,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0.4081</v>
+        <v>0.4021</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -41571,7 +41043,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0.5735</v>
+        <v>0.5682</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -41637,7 +41109,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0.4507</v>
+        <v>0.4721</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -41646,7 +41118,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>expansao</t>
         </is>
       </c>
     </row>
@@ -41703,7 +41175,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0.4851</v>
+        <v>0.4809</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -41769,7 +41241,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0.3065</v>
+        <v>0.3008</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -41877,7 +41349,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0.5122</v>
+        <v>0.507</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -41989,7 +41461,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0.4701</v>
+        <v>0.4679</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -42082,7 +41554,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -42097,15 +41569,15 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0.5047</v>
+        <v>0.4894</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -42167,7 +41639,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0.456</v>
+        <v>0.4456</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -42325,7 +41797,7 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0.4524</v>
+        <v>0.4496</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -42421,7 +41893,7 @@
         <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
@@ -42437,7 +41909,7 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0.4936</v>
+        <v>0.487</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -42446,7 +41918,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>compressao</t>
+          <t>neutro_zona_cinza</t>
         </is>
       </c>
     </row>
@@ -42503,7 +41975,7 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0.5029</v>
+        <v>0.5004</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -42569,7 +42041,7 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0.3904</v>
+        <v>0.3892</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -42578,7 +42050,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>expansao</t>
+          <t>neutro_zona_cinza</t>
         </is>
       </c>
     </row>
@@ -42635,7 +42107,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0.5104</v>
+        <v>0.4906</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -42692,12 +42164,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -42951,7 +42423,7 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0.3908</v>
+        <v>0.3882</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -43017,7 +42489,7 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0.4112</v>
+        <v>0.4106</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -43064,7 +42536,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
@@ -43079,15 +42551,15 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0.4437</v>
+        <v>0.4935</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -43149,7 +42621,7 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0.481</v>
+        <v>0.4816</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -43353,7 +42825,7 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0.4713</v>
+        <v>0.4624</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -43419,7 +42891,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.5188</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -43485,7 +42957,7 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0.3546</v>
+        <v>0.352</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -43551,7 +43023,7 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0.5564</v>
+        <v>0.5522</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -43617,7 +43089,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0.4282</v>
+        <v>0.4318</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -43913,7 +43385,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -44301,7 +43773,7 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0.415</v>
+        <v>0.4144</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -44413,7 +43885,7 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0.3921</v>
+        <v>0.3881</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -44479,7 +43951,7 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0.4123</v>
+        <v>0.4127</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -44587,7 +44059,7 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0.4818</v>
+        <v>0.483</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -44653,7 +44125,7 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0.3844</v>
+        <v>0.3804</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -44761,7 +44233,7 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0.3134</v>
+        <v>0.3116</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -44873,7 +44345,7 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0.4546</v>
+        <v>0.4572</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -44939,7 +44411,7 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0.3999</v>
+        <v>0.4118</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -45269,7 +44741,7 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0.6371</v>
+        <v>0.6384</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -45469,7 +44941,7 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0.5161</v>
+        <v>0.5276</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -45535,7 +45007,7 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>0.4445</v>
+        <v>0.4467</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -45601,7 +45073,7 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0.6135</v>
+        <v>0.6122</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -45713,7 +45185,7 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0.3849</v>
+        <v>0.3845</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -45779,7 +45251,7 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0.5312</v>
+        <v>0.5224</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -45891,7 +45363,7 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0.405</v>
+        <v>0.3987</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -46003,7 +45475,7 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0.4216</v>
+        <v>0.431</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -46229,7 +45701,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -46239,7 +45711,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -46259,7 +45731,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -46289,7 +45761,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -46329,7 +45801,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30">
@@ -46349,7 +45821,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="32">
